--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Regular Savings Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Regular Savings Fund.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA39FD8-EAA6-4AC6-8B1E-CAB6E51ECCCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E314FCB7-6C8C-4BCF-903A-4EB545087E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="314">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Regular Savings Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -76,6 +76,15 @@
     <t>Banks</t>
   </si>
   <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
     <t>Maruti Suzuki India Ltd.</t>
   </si>
   <si>
@@ -94,13 +103,10 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>Insurance</t>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
   </si>
   <si>
     <t>Axis Bank Ltd.</t>
@@ -118,6 +124,42 @@
     <t>Power</t>
   </si>
   <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>Gland Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE068V01023</t>
+  </si>
+  <si>
+    <t>Affle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE00WC01027</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
     <t>Hindustan Unilever Ltd.</t>
   </si>
   <si>
@@ -127,277 +169,268 @@
     <t>Diversified Fmcg</t>
   </si>
   <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
+    <t>Aurobindo Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE406A01037</t>
+  </si>
+  <si>
+    <t>Infosys Ltd.</t>
+  </si>
+  <si>
+    <t>INE009A01021</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE095A01012</t>
+  </si>
+  <si>
+    <t>TBO Tek Ltd.</t>
+  </si>
+  <si>
+    <t>INE673O01025</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Chemplast Sanmar Ltd</t>
+  </si>
+  <si>
+    <t>INE488A01050</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>Alkem Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE540L01014</t>
+  </si>
+  <si>
+    <t>Dabur India Ltd.</t>
+  </si>
+  <si>
+    <t>INE016A01026</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Nuvoco Vistas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE118D01016</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>PVR INOX Ltd.</t>
+  </si>
+  <si>
+    <t>INE191H01014</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Yatra Online Ltd</t>
+  </si>
+  <si>
+    <t>INE0JR601024</t>
+  </si>
+  <si>
+    <t>DLF Ltd.</t>
+  </si>
+  <si>
+    <t>INE271C01023</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>Tata Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE155A01022</t>
+  </si>
+  <si>
+    <t>Oil India Ltd.</t>
+  </si>
+  <si>
+    <t>INE274J01014</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Carborundum Universal Ltd.</t>
+  </si>
+  <si>
+    <t>INE120A01034</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>Mold-Tek Packaging Ltd</t>
+  </si>
+  <si>
+    <t>INE893J01029</t>
+  </si>
+  <si>
+    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE213A01029</t>
+  </si>
+  <si>
+    <t>UPL Ltd.</t>
+  </si>
+  <si>
+    <t>INE628A01036</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>Apollo Tyres Ltd.</t>
+  </si>
+  <si>
+    <t>INE438A01022</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Medi Assist Healthcare Services Ltd</t>
+  </si>
+  <si>
+    <t>INE456Z01021</t>
+  </si>
+  <si>
+    <t>Adani Wilmar Ltd</t>
+  </si>
+  <si>
+    <t>INE699H01024</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
+    <t>Vedant Fashions Ltd.</t>
+  </si>
+  <si>
+    <t>INE825V01034</t>
   </si>
   <si>
     <t>Retailing</t>
   </si>
   <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A01034</t>
-  </si>
-  <si>
-    <t>Gland Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE068V01023</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A01012</t>
-  </si>
-  <si>
-    <t>Chemplast Sanmar Ltd</t>
-  </si>
-  <si>
-    <t>INE488A01050</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Infosys Ltd.</t>
-  </si>
-  <si>
-    <t>INE009A01021</t>
-  </si>
-  <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Affle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE00WC01027</t>
-  </si>
-  <si>
-    <t>It - Services</t>
-  </si>
-  <si>
-    <t>UPL Ltd.</t>
-  </si>
-  <si>
-    <t>INE628A01036</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Dabur India Ltd.</t>
-  </si>
-  <si>
-    <t>INE016A01026</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>Alkem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE540L01014</t>
-  </si>
-  <si>
-    <t>Vishal Mega Mart Ltd.</t>
-  </si>
-  <si>
-    <t>INE01EA01019</t>
-  </si>
-  <si>
-    <t>PVR INOX Ltd.</t>
-  </si>
-  <si>
-    <t>INE191H01014</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Nuvoco Vistas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE118D01016</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>PSP Projects Ltd</t>
-  </si>
-  <si>
-    <t>INE488V01015</t>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
+    <t>CIE Automotive India Ltd</t>
+  </si>
+  <si>
+    <t>INE536H01010</t>
+  </si>
+  <si>
+    <t>Divgi Torqtransfer Systems Ltd</t>
+  </si>
+  <si>
+    <t>INE753U01022</t>
+  </si>
+  <si>
+    <t>Indian Energy Exchange Ltd.</t>
+  </si>
+  <si>
+    <t>INE022Q01020</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Jubilant Ingrevia Ltd.</t>
+  </si>
+  <si>
+    <t>INE0BY001018</t>
+  </si>
+  <si>
+    <t>Tata Communications Ltd.</t>
+  </si>
+  <si>
+    <t>INE151A01013</t>
+  </si>
+  <si>
+    <t>Gujarat Alkalies and Chemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE186A01019</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Teamlease Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE985S01024</t>
+  </si>
+  <si>
+    <t>Commercial Services &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Sai Silks (Kalamandir) Ltd.</t>
+  </si>
+  <si>
+    <t>INE438K01021</t>
+  </si>
+  <si>
+    <t>GNA Axles Ltd</t>
+  </si>
+  <si>
+    <t>INE934S01014</t>
+  </si>
+  <si>
+    <t>Route Mobile Ltd.</t>
+  </si>
+  <si>
+    <t>INE450U01017</t>
+  </si>
+  <si>
+    <t>PNC Infratech Ltd.</t>
+  </si>
+  <si>
+    <t>INE195J01029</t>
   </si>
   <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>Yatra Online Ltd</t>
-  </si>
-  <si>
-    <t>INE0JR601024</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Tata Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE155A01022</t>
-  </si>
-  <si>
-    <t>Adani Wilmar Ltd</t>
-  </si>
-  <si>
-    <t>INE699H01024</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>Apollo Tyres Ltd.</t>
-  </si>
-  <si>
-    <t>INE438A01022</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Bharat Forge Ltd.</t>
-  </si>
-  <si>
-    <t>INE465A01025</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Hyundai Motor India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0V6F01027</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
-    <t>Divgi Torqtransfer Systems Ltd</t>
-  </si>
-  <si>
-    <t>INE753U01022</t>
-  </si>
-  <si>
-    <t>CIE Automotive India Ltd</t>
-  </si>
-  <si>
-    <t>INE536H01010</t>
-  </si>
-  <si>
-    <t>Indian Energy Exchange Ltd.</t>
-  </si>
-  <si>
-    <t>INE022Q01020</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Mold-Tek Packaging Ltd</t>
-  </si>
-  <si>
-    <t>INE893J01029</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Jubilant Ingrevia Ltd.</t>
-  </si>
-  <si>
-    <t>INE0BY001018</t>
-  </si>
-  <si>
-    <t>Gujarat Alkalies and Chemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE186A01019</t>
-  </si>
-  <si>
-    <t>Oil India Ltd.</t>
-  </si>
-  <si>
-    <t>INE274J01014</t>
-  </si>
-  <si>
-    <t>Oil</t>
+    <t>Rategain Travel Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE0CLI01024</t>
+  </si>
+  <si>
+    <t>Sagar Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE229C01021</t>
   </si>
   <si>
     <t>Orient Electric Ltd.</t>
@@ -409,88 +442,10 @@
     <t>Consumer Durables</t>
   </si>
   <si>
-    <t>Jindal Stainless Ltd.</t>
-  </si>
-  <si>
-    <t>INE220G01021</t>
-  </si>
-  <si>
-    <t>GNA Axles Ltd</t>
-  </si>
-  <si>
-    <t>INE934S01014</t>
-  </si>
-  <si>
-    <t>Chennai Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE178A01016</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>Sai Silks (Kalamandir) Ltd.</t>
-  </si>
-  <si>
-    <t>INE438K01021</t>
-  </si>
-  <si>
-    <t>Teamlease Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE985S01024</t>
-  </si>
-  <si>
-    <t>Commercial Services &amp; Supplies</t>
-  </si>
-  <si>
-    <t>PNC Infratech Ltd.</t>
-  </si>
-  <si>
-    <t>INE195J01029</t>
-  </si>
-  <si>
-    <t>Route Mobile Ltd.</t>
-  </si>
-  <si>
-    <t>INE450U01017</t>
-  </si>
-  <si>
-    <t>Sagar Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE229C01021</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE749A01030</t>
-  </si>
-  <si>
-    <t>Bata India Ltd.</t>
-  </si>
-  <si>
-    <t>INE176A01028</t>
-  </si>
-  <si>
-    <t>CEAT Ltd.</t>
-  </si>
-  <si>
-    <t>INE482A01020</t>
-  </si>
-  <si>
-    <t>NIIT Learning Systems Ltd</t>
-  </si>
-  <si>
-    <t>INE342G01023</t>
-  </si>
-  <si>
-    <t>Other Consumer Services</t>
-  </si>
-  <si>
-    <t>^</t>
+    <t>Galaxy Surfactants Ltd.</t>
+  </si>
+  <si>
+    <t>INE600K01018</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -505,7 +460,7 @@
     <t>Government Securities</t>
   </si>
   <si>
-    <t>IN0020230085</t>
+    <t>IN0020240126</t>
   </si>
   <si>
     <t>SOV</t>
@@ -514,15 +469,33 @@
     <t>IN0020210137</t>
   </si>
   <si>
-    <t>IN0020220037</t>
+    <t>IN0020240019</t>
+  </si>
+  <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920240257</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
   </si>
   <si>
     <t>IN0020220151</t>
   </si>
   <si>
-    <t>IN0020240019</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
@@ -562,7 +535,16 @@
     <t>ICRA A</t>
   </si>
   <si>
-    <t>Godrej Industries Ltd. **</t>
+    <t>Godrej Properties Ltd. **</t>
+  </si>
+  <si>
+    <t>INE484J08089</t>
+  </si>
+  <si>
+    <t>ICRA AA+</t>
+  </si>
+  <si>
+    <t>Godrej Industries Ltd.</t>
   </si>
   <si>
     <t>INE233A08139</t>
@@ -571,13 +553,10 @@
     <t>CRISIL AA+</t>
   </si>
   <si>
-    <t>Godrej Properties Ltd. **</t>
-  </si>
-  <si>
-    <t>INE484J08089</t>
-  </si>
-  <si>
-    <t>ICRA AA+</t>
+    <t>NABARD **</t>
+  </si>
+  <si>
+    <t>INE261F08DV4</t>
   </si>
   <si>
     <t>Eris Lifesciences Ltd. **</t>
@@ -586,7 +565,7 @@
     <t>INE406M08029</t>
   </si>
   <si>
-    <t>FITCH AA-</t>
+    <t>FITCH AA</t>
   </si>
   <si>
     <t>INE406M08011</t>
@@ -598,45 +577,39 @@
     <t>INE410P08016</t>
   </si>
   <si>
-    <t>IIFL Home Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE477L07AW0</t>
+    <t>Indostar Capital Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE896L07AF6</t>
+  </si>
+  <si>
+    <t>CARE AA-</t>
+  </si>
+  <si>
+    <t>Bharti Telecom Ltd. **</t>
+  </si>
+  <si>
+    <t>INE403D08207</t>
+  </si>
+  <si>
+    <t>Ashiana Housing Ltd. **</t>
+  </si>
+  <si>
+    <t>INE365D07085</t>
+  </si>
+  <si>
+    <t>CARE A</t>
+  </si>
+  <si>
+    <t>JM Financial Products Ltd. **</t>
+  </si>
+  <si>
+    <t>INE523H07CB9</t>
   </si>
   <si>
     <t>CRISIL AA</t>
   </si>
   <si>
-    <t>Indostar Capital Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE896L07AF6</t>
-  </si>
-  <si>
-    <t>CARE AA-</t>
-  </si>
-  <si>
-    <t>Bharti Telecom Ltd. **</t>
-  </si>
-  <si>
-    <t>INE403D08207</t>
-  </si>
-  <si>
-    <t>Ashiana Housing Ltd. **</t>
-  </si>
-  <si>
-    <t>INE365D07085</t>
-  </si>
-  <si>
-    <t>CARE A</t>
-  </si>
-  <si>
-    <t>JM Financial Products Ltd. **</t>
-  </si>
-  <si>
-    <t>INE523H07CB9</t>
-  </si>
-  <si>
     <t>Prism Johnson Ltd. **</t>
   </si>
   <si>
@@ -649,12 +622,33 @@
     <t>INE010A08149</t>
   </si>
   <si>
+    <t>Vedanta Ltd. **</t>
+  </si>
+  <si>
+    <t>INE205A08038</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE115A07RF8</t>
+  </si>
+  <si>
     <t>JM Financial Credit Solution Ltd. **</t>
   </si>
   <si>
     <t>INE651J07986</t>
   </si>
   <si>
+    <t>Oberoi Realty Ltd. **</t>
+  </si>
+  <si>
+    <t>INE093I07074</t>
+  </si>
+  <si>
+    <t>CARE AA+</t>
+  </si>
+  <si>
     <t>Aavas Financiers Ltd. **</t>
   </si>
   <si>
@@ -664,144 +658,132 @@
     <t>CARE AA</t>
   </si>
   <si>
-    <t>INE896L07868</t>
+    <t>Aadhar Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE883F07314</t>
+  </si>
+  <si>
+    <t>Tata Projects Ltd. **</t>
+  </si>
+  <si>
+    <t>INE725H08246</t>
+  </si>
+  <si>
+    <t>Shriram Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE721A07RR8</t>
+  </si>
+  <si>
+    <t>Torrent Power Ltd. **</t>
+  </si>
+  <si>
+    <t>INE813H07192</t>
+  </si>
+  <si>
+    <t>Aptus Value Housing Finance India Ltd. **</t>
+  </si>
+  <si>
+    <t>INE852O07147</t>
+  </si>
+  <si>
+    <t>INE216P07217</t>
+  </si>
+  <si>
+    <t>Mankind Pharma Ltd **</t>
+  </si>
+  <si>
+    <t>INE634S07017</t>
+  </si>
+  <si>
+    <t>Bamboo Hotels &amp; Global Centre (Delhi) Pvt Ltd. **</t>
+  </si>
+  <si>
+    <t>INE755L07015</t>
+  </si>
+  <si>
+    <t>ICRA A+(CE)</t>
+  </si>
+  <si>
+    <t>Avanse Financial Services Ltd **</t>
+  </si>
+  <si>
+    <t>INE087P07444</t>
   </si>
   <si>
     <t>CRISIL AA-</t>
   </si>
   <si>
-    <t>Aadhar Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE883F07314</t>
-  </si>
-  <si>
-    <t>Shriram Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE721A07RR8</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd. **</t>
-  </si>
-  <si>
-    <t>INE093I07074</t>
-  </si>
-  <si>
-    <t>CARE AA+</t>
-  </si>
-  <si>
-    <t>Torrent Power Ltd. **</t>
-  </si>
-  <si>
-    <t>INE813H07192</t>
-  </si>
-  <si>
-    <t>Aptus Value Housing Finance India Ltd. **</t>
-  </si>
-  <si>
-    <t>INE852O07147</t>
-  </si>
-  <si>
-    <t>INE216P07217</t>
-  </si>
-  <si>
-    <t>Mankind Pharma Ltd **</t>
-  </si>
-  <si>
-    <t>INE634S07017</t>
-  </si>
-  <si>
-    <t>Avanse Financial Services Ltd **</t>
-  </si>
-  <si>
-    <t>INE087P07444</t>
-  </si>
-  <si>
-    <t>Bamboo Hotels &amp; Global Centre (Delhi) Pvt Ltd. **</t>
-  </si>
-  <si>
-    <t>INE755L07015</t>
-  </si>
-  <si>
-    <t>ICRA A+(CE)</t>
-  </si>
-  <si>
     <t>DME Development Ltd. **</t>
   </si>
   <si>
     <t>INE0J7Q07017</t>
   </si>
   <si>
+    <t>INE403D08181</t>
+  </si>
+  <si>
+    <t>Kogta Financial (India) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE192U07343</t>
+  </si>
+  <si>
+    <t>ICRA A+</t>
+  </si>
+  <si>
     <t>Macrotech Developers Ltd. **</t>
   </si>
   <si>
     <t>INE670K07265</t>
   </si>
   <si>
-    <t>ICRA AA-</t>
-  </si>
-  <si>
-    <t>INE233A08097</t>
-  </si>
-  <si>
-    <t>INE403D08181</t>
-  </si>
-  <si>
-    <t>INE528G08279</t>
-  </si>
-  <si>
-    <t>Kogta Financial (India) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE192U07343</t>
-  </si>
-  <si>
-    <t>ICRA A+</t>
-  </si>
-  <si>
     <t>INE0J7Q07074</t>
   </si>
   <si>
     <t>INE0J7Q07082</t>
   </si>
   <si>
+    <t>INE0J7Q07058</t>
+  </si>
+  <si>
+    <t>INE0J7Q07025</t>
+  </si>
+  <si>
+    <t>INE0J7Q07033</t>
+  </si>
+  <si>
     <t>INE0J7Q07066</t>
   </si>
   <si>
-    <t>INE0J7Q07058</t>
-  </si>
-  <si>
     <t>INE0J7Q07041</t>
   </si>
   <si>
-    <t>INE0J7Q07033</t>
-  </si>
-  <si>
-    <t>INE0J7Q07025</t>
-  </si>
-  <si>
     <t>INE0J7Q07108</t>
   </si>
   <si>
+    <t>INE261F08EK5</t>
+  </si>
+  <si>
     <t>Sheela Foam Ltd. **</t>
   </si>
   <si>
     <t>INE916U08012</t>
   </si>
   <si>
-    <t>FITCH AA</t>
-  </si>
-  <si>
     <t>INE916U08038</t>
   </si>
   <si>
-    <t>INE916U08046</t>
-  </si>
-  <si>
     <t>INE916U08020</t>
   </si>
   <si>
+    <t>INE192U07350</t>
+  </si>
+  <si>
+    <t>CARE A+</t>
+  </si>
+  <si>
     <t>INE634S07025</t>
   </si>
   <si>
@@ -817,18 +799,18 @@
     <t>India Universal Trust AL2 **</t>
   </si>
   <si>
+    <t>INE1CBK15037</t>
+  </si>
+  <si>
+    <t>CRISIL AAA(SO)</t>
+  </si>
+  <si>
+    <t>INE1CBK15029</t>
+  </si>
+  <si>
     <t>INE1CBK15011</t>
   </si>
   <si>
-    <t>CRISIL AAA(SO)</t>
-  </si>
-  <si>
-    <t>INE1CBK15037</t>
-  </si>
-  <si>
-    <t>INE1CBK15029</t>
-  </si>
-  <si>
     <t>Term Deposits</t>
   </si>
   <si>
@@ -844,37 +826,40 @@
     <t>Certificate of Deposits</t>
   </si>
   <si>
+    <t>Small Industries Development Bank Of India. **</t>
+  </si>
+  <si>
+    <t>INE556F16BD2</t>
+  </si>
+  <si>
+    <t>CRISIL A1+</t>
+  </si>
+  <si>
+    <t>Export-Import Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE514E16CL5</t>
+  </si>
+  <si>
+    <t>INE514E16CJ9</t>
+  </si>
+  <si>
     <t>HDFC Bank Ltd. **</t>
   </si>
   <si>
-    <t>INE040A16ER2</t>
-  </si>
-  <si>
-    <t>CRISIL A1+</t>
-  </si>
-  <si>
-    <t>Punjab National Bank</t>
-  </si>
-  <si>
-    <t>INE160A16OM8</t>
-  </si>
-  <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A16MT4</t>
-  </si>
-  <si>
-    <t>Bank Of India **</t>
-  </si>
-  <si>
-    <t>INE084A16CN3</t>
-  </si>
-  <si>
-    <t>Kotak Mahindra Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE237A166W0</t>
+    <t>INE040A16GF2</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE238AD6AN0</t>
+  </si>
+  <si>
+    <t>INE261F16975</t>
+  </si>
+  <si>
+    <t>INE040A16GS5</t>
   </si>
   <si>
     <t>Commercial Papers</t>
@@ -937,7 +922,7 @@
     <t>Stock / Index Futures</t>
   </si>
   <si>
-    <t>Bata India Ltd. $$</t>
+    <t>IndusInd Bank Ltd. $$</t>
   </si>
   <si>
     <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
@@ -952,9 +937,6 @@
     <t>$$ - Derivatives.</t>
   </si>
   <si>
-    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
-  </si>
-  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
@@ -964,7 +946,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -986,15 +968,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="##0.00"/>
     <numFmt numFmtId="165" formatCode="##0.00%"/>
-    <numFmt numFmtId="166" formatCode="\^"/>
-    <numFmt numFmtId="167" formatCode="##0"/>
+    <numFmt numFmtId="166" formatCode="##0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1181,7 +1162,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
@@ -1235,16 +1216,13 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1316,7 +1294,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="38300025"/>
+          <a:off x="666750" y="38223825"/>
           <a:ext cx="3705225" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1363,7 +1341,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="41157525"/>
+          <a:off x="666750" y="41081325"/>
           <a:ext cx="3705225" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1702,16 +1680,16 @@
   <dimension ref="A1:J210"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="27" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="55.5703125" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.85546875" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="47.140625" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="11.140625" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="38.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="11.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="29.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="26.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="10" style="26" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="55.5703125" style="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.85546875" style="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.7109375" style="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="47.140625" style="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="11.140625" style="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="38.7109375" style="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="11.7109375" style="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="29.7109375" style="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="26.7109375" style="26" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1799,10 +1777,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="13">
-        <v>68231.26999999999</v>
+        <v>70830.920000000027</v>
       </c>
       <c r="H5" s="14">
-        <v>0.21701745221829991</v>
+        <v>0.22214646938890004</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>13</v>
@@ -1836,10 +1814,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="13">
-        <v>68231.26999999999</v>
+        <v>70830.920000000027</v>
       </c>
       <c r="H7" s="14">
-        <v>0.21701745221829991</v>
+        <v>0.22214646938890004</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>13</v>
@@ -1862,13 +1840,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="18">
-        <v>489871</v>
+        <v>372298</v>
       </c>
       <c r="G8" s="19">
-        <v>6137.1</v>
+        <v>5382.68</v>
       </c>
       <c r="H8" s="20">
-        <v>1.9519756938699999E-2</v>
+        <v>1.6881657867200001E-2</v>
       </c>
       <c r="I8" s="19" t="s">
         <v>13</v>
@@ -1891,13 +1869,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="18">
-        <v>29292</v>
+        <v>238704</v>
       </c>
       <c r="G9" s="19">
-        <v>3606.04</v>
+        <v>4325.79</v>
       </c>
       <c r="H9" s="20">
-        <v>1.14694276305E-2</v>
+        <v>1.35669418924E-2</v>
       </c>
       <c r="I9" s="19" t="s">
         <v>13</v>
@@ -1920,13 +1898,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="18">
-        <v>203104</v>
+        <v>29292</v>
       </c>
       <c r="G10" s="19">
-        <v>3542.03</v>
+        <v>3608.48</v>
       </c>
       <c r="H10" s="20">
-        <v>1.1265836416199999E-2</v>
+        <v>1.13172480587E-2</v>
       </c>
       <c r="I10" s="19" t="s">
         <v>13</v>
@@ -1949,13 +1927,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="18">
-        <v>232733</v>
+        <v>203104</v>
       </c>
       <c r="G11" s="19">
-        <v>3452.83</v>
+        <v>3407.27</v>
       </c>
       <c r="H11" s="20">
-        <v>1.0982125491E-2</v>
+        <v>1.06861946839E-2</v>
       </c>
       <c r="I11" s="19" t="s">
         <v>13</v>
@@ -1978,13 +1956,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="18">
-        <v>250412</v>
+        <v>170149</v>
       </c>
       <c r="G12" s="19">
-        <v>2469.31</v>
+        <v>3309.23</v>
       </c>
       <c r="H12" s="20">
-        <v>7.8539262853999994E-3</v>
+        <v>1.03787125863E-2</v>
       </c>
       <c r="I12" s="19" t="s">
         <v>13</v>
@@ -2004,16 +1982,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F13" s="18">
-        <v>694975</v>
+        <v>250412</v>
       </c>
       <c r="G13" s="19">
-        <v>2251.7199999999998</v>
+        <v>2985.41</v>
       </c>
       <c r="H13" s="20">
-        <v>7.1618561037000003E-3</v>
+        <v>9.3631184119000004E-3</v>
       </c>
       <c r="I13" s="19" t="s">
         <v>13</v>
@@ -2024,25 +2002,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>34</v>
-      </c>
       <c r="F14" s="18">
-        <v>90560</v>
+        <v>817276</v>
       </c>
       <c r="G14" s="19">
-        <v>2235.75</v>
+        <v>2728.88</v>
       </c>
       <c r="H14" s="20">
-        <v>7.1110616700999999E-3</v>
+        <v>8.5585653466999992E-3</v>
       </c>
       <c r="I14" s="19" t="s">
         <v>13</v>
@@ -2053,25 +2031,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>36</v>
-      </c>
       <c r="D15" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F15" s="18">
-        <v>58133</v>
+        <v>334835</v>
       </c>
       <c r="G15" s="19">
-        <v>2130.37</v>
+        <v>2601.17</v>
       </c>
       <c r="H15" s="20">
-        <v>6.7758883820000001E-3</v>
+        <v>8.1580294564000001E-3</v>
       </c>
       <c r="I15" s="19" t="s">
         <v>13</v>
@@ -2082,25 +2060,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>17</v>
-      </c>
       <c r="F16" s="18">
-        <v>125182</v>
+        <v>139897</v>
       </c>
       <c r="G16" s="19">
-        <v>2126.5300000000002</v>
+        <v>2596.77</v>
       </c>
       <c r="H16" s="20">
-        <v>6.7636748174999999E-3</v>
+        <v>8.1442297703000002E-3</v>
       </c>
       <c r="I16" s="19" t="s">
         <v>13</v>
@@ -2111,25 +2089,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>41</v>
-      </c>
       <c r="D17" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F17" s="18">
-        <v>130009</v>
+        <v>156123</v>
       </c>
       <c r="G17" s="19">
-        <v>1982.31</v>
+        <v>2480.17</v>
       </c>
       <c r="H17" s="20">
-        <v>6.3049664136000001E-3</v>
+        <v>7.7785380874000002E-3</v>
       </c>
       <c r="I17" s="19" t="s">
         <v>13</v>
@@ -2140,25 +2118,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="D18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>26</v>
-      </c>
       <c r="F18" s="18">
-        <v>103328</v>
+        <v>132973</v>
       </c>
       <c r="G18" s="19">
-        <v>1920.35</v>
+        <v>2307.88</v>
       </c>
       <c r="H18" s="20">
-        <v>6.1078954615999999E-3</v>
+        <v>7.2381862861000002E-3</v>
       </c>
       <c r="I18" s="19" t="s">
         <v>13</v>
@@ -2178,16 +2156,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F19" s="18">
-        <v>191885</v>
+        <v>118083</v>
       </c>
       <c r="G19" s="19">
-        <v>1901.96</v>
+        <v>2214.5300000000002</v>
       </c>
       <c r="H19" s="20">
-        <v>6.0494039378999999E-3</v>
+        <v>6.9454133994000002E-3</v>
       </c>
       <c r="I19" s="19" t="s">
         <v>13</v>
@@ -2210,13 +2188,13 @@
         <v>48</v>
       </c>
       <c r="F20" s="18">
-        <v>399277</v>
+        <v>90560</v>
       </c>
       <c r="G20" s="19">
-        <v>1894.97</v>
+        <v>2126.62</v>
       </c>
       <c r="H20" s="20">
-        <v>6.0271714337E-3</v>
+        <v>6.6697019427999996E-3</v>
       </c>
       <c r="I20" s="19" t="s">
         <v>13</v>
@@ -2236,16 +2214,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F21" s="18">
-        <v>151758</v>
+        <v>181447</v>
       </c>
       <c r="G21" s="19">
-        <v>1778.45</v>
+        <v>2082.65</v>
       </c>
       <c r="H21" s="20">
-        <v>5.6565660862000003E-3</v>
+        <v>6.5317991700999996E-3</v>
       </c>
       <c r="I21" s="19" t="s">
         <v>13</v>
@@ -2268,13 +2246,13 @@
         <v>53</v>
       </c>
       <c r="F22" s="18">
-        <v>100942</v>
+        <v>126247</v>
       </c>
       <c r="G22" s="19">
-        <v>1641.62</v>
+        <v>1972.86</v>
       </c>
       <c r="H22" s="20">
-        <v>5.2213624327000002E-3</v>
+        <v>6.1874656378999998E-3</v>
       </c>
       <c r="I22" s="19" t="s">
         <v>13</v>
@@ -2294,16 +2272,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F23" s="18">
-        <v>86818</v>
+        <v>214002</v>
       </c>
       <c r="G23" s="19">
-        <v>1632</v>
+        <v>1748.29</v>
       </c>
       <c r="H23" s="20">
-        <v>5.1907649090999998E-3</v>
+        <v>5.4831484747999999E-3</v>
       </c>
       <c r="I23" s="19" t="s">
         <v>13</v>
@@ -2314,25 +2292,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="D24" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>59</v>
-      </c>
       <c r="F24" s="18">
-        <v>106263</v>
+        <v>130556</v>
       </c>
       <c r="G24" s="19">
-        <v>1602.39</v>
+        <v>1703.36</v>
       </c>
       <c r="H24" s="20">
-        <v>5.0965868767000001E-3</v>
+        <v>5.3422348615000002E-3</v>
       </c>
       <c r="I24" s="19" t="s">
         <v>13</v>
@@ -2343,25 +2321,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="D25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>62</v>
-      </c>
       <c r="F25" s="18">
-        <v>256409</v>
+        <v>399277</v>
       </c>
       <c r="G25" s="19">
-        <v>1548.07</v>
+        <v>1694.73</v>
       </c>
       <c r="H25" s="20">
-        <v>4.9238158290000004E-3</v>
+        <v>5.3151686589E-3</v>
       </c>
       <c r="I25" s="19" t="s">
         <v>13</v>
@@ -2372,25 +2350,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="17" t="s">
-        <v>64</v>
-      </c>
       <c r="D26" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F26" s="18">
-        <v>283147</v>
+        <v>29292</v>
       </c>
       <c r="G26" s="19">
-        <v>1500.25</v>
+        <v>1493.45</v>
       </c>
       <c r="H26" s="20">
-        <v>4.7717187836000003E-3</v>
+        <v>4.6838957436999996E-3</v>
       </c>
       <c r="I26" s="19" t="s">
         <v>13</v>
@@ -2401,25 +2379,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>23</v>
-      </c>
       <c r="F27" s="18">
-        <v>29292</v>
+        <v>283147</v>
       </c>
       <c r="G27" s="19">
-        <v>1483.07</v>
+        <v>1367.46</v>
       </c>
       <c r="H27" s="20">
-        <v>4.7170758050000001E-3</v>
+        <v>4.2887542761000002E-3</v>
       </c>
       <c r="I27" s="19" t="s">
         <v>13</v>
@@ -2430,25 +2408,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="D28" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>37</v>
-      </c>
       <c r="F28" s="18">
-        <v>1314135</v>
+        <v>348764</v>
       </c>
       <c r="G28" s="19">
-        <v>1418.61</v>
+        <v>1248.05</v>
       </c>
       <c r="H28" s="20">
-        <v>4.5120533136000004E-3</v>
+        <v>3.9142496119000001E-3</v>
       </c>
       <c r="I28" s="19" t="s">
         <v>13</v>
@@ -2474,10 +2452,10 @@
         <v>122411</v>
       </c>
       <c r="G29" s="19">
-        <v>1334.89</v>
+        <v>1206.05</v>
       </c>
       <c r="H29" s="20">
-        <v>4.2457721627000003E-3</v>
+        <v>3.7825253351E-3</v>
       </c>
       <c r="I29" s="19" t="s">
         <v>13</v>
@@ -2497,16 +2475,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F30" s="18">
-        <v>348764</v>
+        <v>1047632</v>
       </c>
       <c r="G30" s="19">
-        <v>1222.42</v>
+        <v>1046.69</v>
       </c>
       <c r="H30" s="20">
-        <v>3.8880483089E-3</v>
+        <v>3.2827257933000001E-3</v>
       </c>
       <c r="I30" s="19" t="s">
         <v>13</v>
@@ -2517,25 +2495,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="D31" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>78</v>
-      </c>
       <c r="F31" s="18">
-        <v>182957</v>
+        <v>121049</v>
       </c>
       <c r="G31" s="19">
-        <v>1159.03</v>
+        <v>965.79</v>
       </c>
       <c r="H31" s="20">
-        <v>3.6864290763999998E-3</v>
+        <v>3.0289997457000001E-3</v>
       </c>
       <c r="I31" s="19" t="s">
         <v>13</v>
@@ -2546,25 +2524,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="17" t="s">
-        <v>80</v>
-      </c>
       <c r="D32" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="F32" s="18">
-        <v>1047632</v>
+        <v>133384</v>
       </c>
       <c r="G32" s="19">
-        <v>994.52</v>
+        <v>959.7</v>
       </c>
       <c r="H32" s="20">
-        <v>3.1631859788E-3</v>
+        <v>3.0098997256000001E-3</v>
       </c>
       <c r="I32" s="19" t="s">
         <v>13</v>
@@ -2575,25 +2553,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>26</v>
-      </c>
       <c r="F33" s="18">
-        <v>153778</v>
+        <v>221634</v>
       </c>
       <c r="G33" s="19">
-        <v>981.18</v>
+        <v>945.93</v>
       </c>
       <c r="H33" s="20">
-        <v>3.1207565646000001E-3</v>
+        <v>2.9667129805E-3</v>
       </c>
       <c r="I33" s="19" t="s">
         <v>13</v>
@@ -2604,25 +2582,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="D34" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D34" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>20</v>
-      </c>
       <c r="F34" s="18">
-        <v>133384</v>
+        <v>87629</v>
       </c>
       <c r="G34" s="19">
-        <v>955.16</v>
+        <v>869.1</v>
       </c>
       <c r="H34" s="20">
-        <v>3.0379969427999998E-3</v>
+        <v>2.7257516427000002E-3</v>
       </c>
       <c r="I34" s="19" t="s">
         <v>13</v>
@@ -2642,16 +2620,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F35" s="18">
-        <v>340000</v>
+        <v>125046</v>
       </c>
       <c r="G35" s="19">
-        <v>906.61</v>
+        <v>836.5</v>
       </c>
       <c r="H35" s="20">
-        <v>2.8835780478999999E-3</v>
+        <v>2.6235085135E-3</v>
       </c>
       <c r="I35" s="19" t="s">
         <v>13</v>
@@ -2662,25 +2640,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="17" t="s">
-        <v>90</v>
-      </c>
       <c r="D36" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F36" s="18">
-        <v>198634</v>
+        <v>331080</v>
       </c>
       <c r="G36" s="19">
-        <v>868.63</v>
+        <v>792.61</v>
       </c>
       <c r="H36" s="20">
-        <v>2.7627782615999999E-3</v>
+        <v>2.4858566442999999E-3</v>
       </c>
       <c r="I36" s="19" t="s">
         <v>13</v>
@@ -2691,25 +2669,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>91</v>
-      </c>
       <c r="F37" s="18">
-        <v>68077</v>
+        <v>126118</v>
       </c>
       <c r="G37" s="19">
-        <v>833.3</v>
+        <v>791.89</v>
       </c>
       <c r="H37" s="20">
-        <v>2.6504071070999999E-3</v>
+        <v>2.4835985138E-3</v>
       </c>
       <c r="I37" s="19" t="s">
         <v>13</v>
@@ -2720,25 +2698,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="D38" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D38" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>96</v>
-      </c>
       <c r="F38" s="18">
-        <v>614498</v>
+        <v>166877</v>
       </c>
       <c r="G38" s="19">
-        <v>827.24</v>
+        <v>785.24</v>
       </c>
       <c r="H38" s="20">
-        <v>2.6311325756E-3</v>
+        <v>2.4627421700000002E-3</v>
       </c>
       <c r="I38" s="19" t="s">
         <v>13</v>
@@ -2749,10 +2727,10 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="17" t="s">
         <v>97</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>98</v>
       </c>
       <c r="D39" s="17" t="s">
         <v>13</v>
@@ -2761,13 +2739,13 @@
         <v>20</v>
       </c>
       <c r="F39" s="18">
-        <v>40211</v>
+        <v>131457</v>
       </c>
       <c r="G39" s="19">
-        <v>674.56</v>
+        <v>651.16999999999996</v>
       </c>
       <c r="H39" s="20">
-        <v>2.1455161623999998E-3</v>
+        <v>2.0422594605999998E-3</v>
       </c>
       <c r="I39" s="19" t="s">
         <v>13</v>
@@ -2778,25 +2756,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="D40" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>75</v>
-      </c>
       <c r="F40" s="18">
-        <v>131392</v>
+        <v>235418</v>
       </c>
       <c r="G40" s="19">
-        <v>673.78</v>
+        <v>647.4</v>
       </c>
       <c r="H40" s="20">
-        <v>2.1430352821000002E-3</v>
+        <v>2.0304356385999998E-3</v>
       </c>
       <c r="I40" s="19" t="s">
         <v>13</v>
@@ -2819,13 +2797,13 @@
         <v>103</v>
       </c>
       <c r="F41" s="18">
-        <v>139570</v>
+        <v>80050</v>
       </c>
       <c r="G41" s="19">
-        <v>616.05999999999995</v>
+        <v>638.24</v>
       </c>
       <c r="H41" s="20">
-        <v>1.9594501407999999E-3</v>
+        <v>2.0017072010000002E-3</v>
       </c>
       <c r="I41" s="19" t="s">
         <v>13</v>
@@ -2845,16 +2823,16 @@
         <v>13</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F42" s="18">
         <v>62263</v>
       </c>
       <c r="G42" s="19">
-        <v>604.11</v>
+        <v>579.04999999999995</v>
       </c>
       <c r="H42" s="20">
-        <v>1.9214417826000001E-3</v>
+        <v>1.8160700594999999E-3</v>
       </c>
       <c r="I42" s="19" t="s">
         <v>13</v>
@@ -2874,16 +2852,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F43" s="18">
-        <v>101671</v>
+        <v>127463</v>
       </c>
       <c r="G43" s="19">
-        <v>598.54</v>
+        <v>573.26</v>
       </c>
       <c r="H43" s="20">
-        <v>1.9037257528999999E-3</v>
+        <v>1.797910927E-3</v>
       </c>
       <c r="I43" s="19" t="s">
         <v>13</v>
@@ -2903,16 +2881,16 @@
         <v>13</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F44" s="18">
-        <v>127463</v>
+        <v>101671</v>
       </c>
       <c r="G44" s="19">
-        <v>592</v>
+        <v>566.30999999999995</v>
       </c>
       <c r="H44" s="20">
-        <v>1.8829245257999999E-3</v>
+        <v>1.7761136955E-3</v>
       </c>
       <c r="I44" s="19" t="s">
         <v>13</v>
@@ -2935,13 +2913,13 @@
         <v>112</v>
       </c>
       <c r="F45" s="18">
-        <v>317964</v>
+        <v>266439</v>
       </c>
       <c r="G45" s="19">
-        <v>555.16999999999996</v>
+        <v>534.34</v>
       </c>
       <c r="H45" s="20">
-        <v>1.7657824476000001E-3</v>
+        <v>1.6758464304999999E-3</v>
       </c>
       <c r="I45" s="19" t="s">
         <v>13</v>
@@ -2961,16 +2939,16 @@
         <v>13</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="F46" s="18">
-        <v>99999</v>
+        <v>69072</v>
       </c>
       <c r="G46" s="19">
-        <v>551.84</v>
+        <v>485.16</v>
       </c>
       <c r="H46" s="20">
-        <v>1.7551909972000001E-3</v>
+        <v>1.5216035749000001E-3</v>
       </c>
       <c r="I46" s="19" t="s">
         <v>13</v>
@@ -2981,25 +2959,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="17" t="s">
-        <v>117</v>
-      </c>
       <c r="D47" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="F47" s="18">
-        <v>72792</v>
+        <v>28480</v>
       </c>
       <c r="G47" s="19">
-        <v>543.5</v>
+        <v>477.38</v>
       </c>
       <c r="H47" s="20">
-        <v>1.7286646618E-3</v>
+        <v>1.4972032207999999E-3</v>
       </c>
       <c r="I47" s="19" t="s">
         <v>13</v>
@@ -3010,25 +2988,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F48" s="18">
-        <v>77222</v>
+        <v>70257</v>
       </c>
       <c r="G48" s="19">
-        <v>538.04</v>
+        <v>403.28</v>
       </c>
       <c r="H48" s="20">
-        <v>1.7112984998E-3</v>
+        <v>1.2648039609000001E-3</v>
       </c>
       <c r="I48" s="19" t="s">
         <v>13</v>
@@ -3039,10 +3017,10 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>13</v>
@@ -3051,13 +3029,13 @@
         <v>48</v>
       </c>
       <c r="F49" s="18">
-        <v>73674</v>
+        <v>87449</v>
       </c>
       <c r="G49" s="19">
-        <v>510.63</v>
+        <v>365.58</v>
       </c>
       <c r="H49" s="20">
-        <v>1.624117822E-3</v>
+        <v>1.1465657410000001E-3</v>
       </c>
       <c r="I49" s="19" t="s">
         <v>13</v>
@@ -3068,25 +3046,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C50" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>125</v>
-      </c>
       <c r="F50" s="18">
-        <v>112844</v>
+        <v>18433</v>
       </c>
       <c r="G50" s="19">
-        <v>474.45</v>
+        <v>360.49</v>
       </c>
       <c r="H50" s="20">
-        <v>1.5090431439999999E-3</v>
+        <v>1.1306020132E-3</v>
       </c>
       <c r="I50" s="19" t="s">
         <v>13</v>
@@ -3097,25 +3075,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D51" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F51" s="18">
-        <v>189649</v>
+        <v>277369</v>
       </c>
       <c r="G51" s="19">
-        <v>416.56</v>
+        <v>352.65</v>
       </c>
       <c r="H51" s="20">
-        <v>1.3249172981000001E-3</v>
+        <v>1.1060134814999999E-3</v>
       </c>
       <c r="I51" s="19" t="s">
         <v>13</v>
@@ -3126,25 +3104,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D52" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F52" s="18">
-        <v>59023</v>
+        <v>96762</v>
       </c>
       <c r="G52" s="19">
-        <v>385.6</v>
+        <v>331.07</v>
       </c>
       <c r="H52" s="20">
-        <v>1.2264454344E-3</v>
+        <v>1.0383322936000001E-3</v>
       </c>
       <c r="I52" s="19" t="s">
         <v>13</v>
@@ -3155,25 +3133,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="16" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D53" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="F53" s="18">
-        <v>96762</v>
+        <v>33564</v>
       </c>
       <c r="G53" s="19">
-        <v>346.07</v>
+        <v>318.61</v>
       </c>
       <c r="H53" s="20">
-        <v>1.1007156936999999E-3</v>
+        <v>9.9925409139999997E-4</v>
       </c>
       <c r="I53" s="19" t="s">
         <v>13</v>
@@ -3184,25 +3162,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D54" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F54" s="18">
-        <v>53667</v>
+        <v>85156</v>
       </c>
       <c r="G54" s="19">
-        <v>290.58</v>
+        <v>248.61</v>
       </c>
       <c r="H54" s="20">
-        <v>9.2422332549999995E-4</v>
+        <v>7.7971363E-4</v>
       </c>
       <c r="I54" s="19" t="s">
         <v>13</v>
@@ -3213,25 +3191,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="16" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D55" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F55" s="18">
-        <v>164565</v>
+        <v>55441</v>
       </c>
       <c r="G55" s="19">
-        <v>278.48</v>
+        <v>246.05</v>
       </c>
       <c r="H55" s="20">
-        <v>8.8573787490000004E-4</v>
+        <v>7.7168472170000002E-4</v>
       </c>
       <c r="I55" s="19" t="s">
         <v>13</v>
@@ -3242,25 +3220,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="16" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D56" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="F56" s="18">
-        <v>11169</v>
+        <v>98558</v>
       </c>
       <c r="G56" s="19">
-        <v>272.76</v>
+        <v>236.65</v>
       </c>
       <c r="H56" s="20">
-        <v>8.675447528E-4</v>
+        <v>7.4220357410000005E-4</v>
       </c>
       <c r="I56" s="19" t="s">
         <v>13</v>
@@ -3271,25 +3249,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D57" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="F57" s="18">
-        <v>85156</v>
+        <v>88054</v>
       </c>
       <c r="G57" s="19">
-        <v>271.64999999999998</v>
+        <v>199.79</v>
       </c>
       <c r="H57" s="20">
-        <v>8.6401426930000002E-4</v>
+        <v>6.265998397E-4</v>
       </c>
       <c r="I57" s="19" t="s">
         <v>13</v>
@@ -3300,25 +3278,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D58" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F58" s="18">
-        <v>19068</v>
+        <v>1327</v>
       </c>
       <c r="G58" s="19">
-        <v>228.24</v>
+        <v>30.6</v>
       </c>
       <c r="H58" s="20">
-        <v>7.2594373950000003E-4</v>
+        <v>9.5970544499999997E-5</v>
       </c>
       <c r="I58" s="19" t="s">
         <v>13</v>
@@ -3329,27 +3307,6 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" s="18">
-        <v>88597</v>
-      </c>
-      <c r="G59" s="19">
-        <v>183.24</v>
-      </c>
-      <c r="H59" s="20">
-        <v>5.8281603059999996E-4</v>
-      </c>
-      <c r="I59" s="19" t="s">
         <v>13</v>
       </c>
       <c r="J59" s="15" t="s">
@@ -3357,28 +3314,28 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="F60" s="18">
-        <v>21552</v>
-      </c>
-      <c r="G60" s="19">
-        <v>170.59</v>
-      </c>
-      <c r="H60" s="20">
-        <v>5.4258124130000004E-4</v>
-      </c>
-      <c r="I60" s="19" t="s">
+      <c r="B60" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J60" s="15" t="s">
@@ -3387,27 +3344,6 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="D61" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="F61" s="18">
-        <v>4611</v>
-      </c>
-      <c r="G61" s="19">
-        <v>59.8</v>
-      </c>
-      <c r="H61" s="20">
-        <v>1.9020082200000001E-4</v>
-      </c>
-      <c r="I61" s="19" t="s">
         <v>13</v>
       </c>
       <c r="J61" s="15" t="s">
@@ -3415,28 +3351,28 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="F62" s="18">
-        <v>1819</v>
-      </c>
-      <c r="G62" s="19">
-        <v>51.96</v>
-      </c>
-      <c r="H62" s="20">
-        <v>1.6526479450000001E-4</v>
-      </c>
-      <c r="I62" s="19" t="s">
+      <c r="B62" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="13">
+        <v>195708.41999999998</v>
+      </c>
+      <c r="H62" s="14">
+        <v>0.61379881177550022</v>
+      </c>
+      <c r="I62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J62" s="15" t="s">
@@ -3445,27 +3381,6 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D63" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="F63" s="18">
-        <v>923</v>
-      </c>
-      <c r="G63" s="19">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="H63" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="I63" s="19" t="s">
         <v>13</v>
       </c>
       <c r="J63" s="15" t="s">
@@ -3473,7 +3388,28 @@
       </c>
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="13">
+        <v>191411.16</v>
+      </c>
+      <c r="H64" s="14">
+        <v>0.60032134830270023</v>
+      </c>
+      <c r="I64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J64" s="15" t="s">
@@ -3481,28 +3417,7 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H65" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="I65" s="13" t="s">
+      <c r="B65" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J65" s="15" t="s">
@@ -3510,7 +3425,28 @@
       </c>
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="13">
+        <v>61276.5</v>
+      </c>
+      <c r="H66" s="14">
+        <v>0.19218101546109997</v>
+      </c>
+      <c r="I66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J66" s="15" t="s">
@@ -3518,29 +3454,29 @@
       </c>
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="13">
-        <v>193264.47999999995</v>
-      </c>
-      <c r="H67" s="14">
-        <v>0.61470004961419988</v>
-      </c>
-      <c r="I67" s="13" t="s">
-        <v>13</v>
+      <c r="B67" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D67" s="21">
+        <v>6.79</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F67" s="18">
+        <v>28854150</v>
+      </c>
+      <c r="G67" s="19">
+        <v>29890.85</v>
+      </c>
+      <c r="H67" s="20">
+        <v>9.3746442861499996E-2</v>
+      </c>
+      <c r="I67" s="19">
+        <v>6.37</v>
       </c>
       <c r="J67" s="15" t="s">
         <v>13</v>
@@ -3548,36 +3484,57 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="16" t="s">
-        <v>13</v>
+        <v>145</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="D68" s="21">
+        <v>6.99</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F68" s="18">
+        <v>16574750</v>
+      </c>
+      <c r="G68" s="19">
+        <v>16918.91</v>
+      </c>
+      <c r="H68" s="20">
+        <v>5.3062647251400002E-2</v>
+      </c>
+      <c r="I68" s="19">
+        <v>6.8</v>
       </c>
       <c r="J68" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="13">
-        <v>188502.43999999992</v>
-      </c>
-      <c r="H69" s="14">
-        <v>0.59955383017319996</v>
-      </c>
-      <c r="I69" s="13" t="s">
-        <v>13</v>
+      <c r="B69" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D69" s="21">
+        <v>7.1</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F69" s="18">
+        <v>10775880</v>
+      </c>
+      <c r="G69" s="19">
+        <v>11359.72</v>
+      </c>
+      <c r="H69" s="20">
+        <v>3.5627402429199997E-2</v>
+      </c>
+      <c r="I69" s="19">
+        <v>6.39</v>
       </c>
       <c r="J69" s="15" t="s">
         <v>13</v>
@@ -3585,36 +3542,57 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="16" t="s">
-        <v>13</v>
+        <v>150</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D70" s="21">
+        <v>7.1400000000000006</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F70" s="18">
+        <v>1000000</v>
+      </c>
+      <c r="G70" s="19">
+        <v>1037.76</v>
+      </c>
+      <c r="H70" s="20">
+        <v>3.254718703E-3</v>
+      </c>
+      <c r="I70" s="19">
+        <v>6.82</v>
       </c>
       <c r="J70" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="13">
-        <v>63386.509999999995</v>
-      </c>
-      <c r="H71" s="14">
-        <v>0.2016081322444</v>
-      </c>
-      <c r="I71" s="13" t="s">
-        <v>13</v>
+      <c r="B71" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D71" s="21">
+        <v>7.12</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F71" s="18">
+        <v>1000000</v>
+      </c>
+      <c r="G71" s="19">
+        <v>1033.6400000000001</v>
+      </c>
+      <c r="H71" s="20">
+        <v>3.2417971786999999E-3</v>
+      </c>
+      <c r="I71" s="19">
+        <v>6.83</v>
       </c>
       <c r="J71" s="15" t="s">
         <v>13</v>
@@ -3622,28 +3600,28 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="16" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="D72" s="22">
-        <v>7.18</v>
+        <v>154</v>
+      </c>
+      <c r="D72" s="21">
+        <v>7.13</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F72" s="18">
-        <v>25815500</v>
+        <v>665600</v>
       </c>
       <c r="G72" s="19">
-        <v>26521.42</v>
+        <v>687.53</v>
       </c>
       <c r="H72" s="20">
-        <v>8.4354446248499998E-2</v>
+        <v>2.1562950488E-3</v>
       </c>
       <c r="I72" s="19">
-        <v>6.87</v>
+        <v>6.75</v>
       </c>
       <c r="J72" s="15" t="s">
         <v>13</v>
@@ -3651,28 +3629,28 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B73" s="16" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="D73" s="22">
-        <v>7.53</v>
+        <v>156</v>
+      </c>
+      <c r="D73" s="21">
+        <v>7.29</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F73" s="18">
-        <v>16574750</v>
+        <v>288800</v>
       </c>
       <c r="G73" s="19">
-        <v>16695.53</v>
+        <v>301.47000000000003</v>
       </c>
       <c r="H73" s="20">
-        <v>5.3102065725499997E-2</v>
+        <v>9.4549804130000001E-4</v>
       </c>
       <c r="I73" s="19">
-        <v>7.47</v>
+        <v>6.88</v>
       </c>
       <c r="J73" s="15" t="s">
         <v>13</v>
@@ -3680,28 +3658,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="16" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="D74" s="22">
-        <v>7.38</v>
+        <v>157</v>
+      </c>
+      <c r="D74" s="21">
+        <v>7.26</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F74" s="18">
-        <v>11500000</v>
+        <v>43850</v>
       </c>
       <c r="G74" s="19">
-        <v>11693.21</v>
+        <v>46.62</v>
       </c>
       <c r="H74" s="20">
-        <v>3.7191607931099997E-2</v>
+        <v>1.4621394720000001E-4</v>
       </c>
       <c r="I74" s="19">
-        <v>6.71</v>
+        <v>6.31</v>
       </c>
       <c r="J74" s="15" t="s">
         <v>13</v>
@@ -3709,57 +3687,36 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="C75" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="D75" s="22">
-        <v>7.26</v>
-      </c>
-      <c r="E75" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F75" s="18">
-        <v>5463150</v>
-      </c>
-      <c r="G75" s="19">
-        <v>5633.67</v>
-      </c>
-      <c r="H75" s="20">
-        <v>1.7918539550100001E-2</v>
-      </c>
-      <c r="I75" s="19">
-        <v>6.86</v>
+        <v>13</v>
       </c>
       <c r="J75" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="D76" s="22">
-        <v>7.1</v>
-      </c>
-      <c r="E76" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F76" s="18">
-        <v>2775880</v>
-      </c>
-      <c r="G76" s="19">
-        <v>2842.68</v>
-      </c>
-      <c r="H76" s="20">
-        <v>9.0414727892000005E-3</v>
-      </c>
-      <c r="I76" s="19">
-        <v>6.86</v>
+      <c r="B76" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="13">
+        <v>130134.66000000002</v>
+      </c>
+      <c r="H76" s="14">
+        <v>0.4081403328415999</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J76" s="15" t="s">
         <v>13</v>
@@ -3767,36 +3724,57 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B77" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="15" t="s">
-        <v>13</v>
+        <v>159</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="D77" s="21">
+        <v>5.83</v>
+      </c>
+      <c r="E77" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="F77" s="18">
+        <v>1000</v>
+      </c>
+      <c r="G77" s="19">
+        <v>9950.0499999999993</v>
+      </c>
+      <c r="H77" s="20">
+        <v>3.1206265254900001E-2</v>
+      </c>
+      <c r="I77" s="19">
+        <v>5.93</v>
+      </c>
+      <c r="J77" s="15">
+        <v>6.88</v>
       </c>
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="13">
-        <v>125115.93000000004</v>
-      </c>
-      <c r="H78" s="14">
-        <v>0.39794569792880002</v>
-      </c>
-      <c r="I78" s="13" t="s">
-        <v>13</v>
+      <c r="B78" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C78" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="D78" s="21">
+        <v>6.58</v>
+      </c>
+      <c r="E78" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="F78" s="18">
+        <v>800</v>
+      </c>
+      <c r="G78" s="19">
+        <v>7981.84</v>
+      </c>
+      <c r="H78" s="20">
+        <v>2.5033383376100001E-2</v>
+      </c>
+      <c r="I78" s="19">
+        <v>6.81</v>
       </c>
       <c r="J78" s="15" t="s">
         <v>13</v>
@@ -3804,57 +3782,57 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="D79" s="22">
-        <v>5.83</v>
+        <v>166</v>
+      </c>
+      <c r="D79" s="21">
+        <v>9.5</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F79" s="18">
-        <v>1000</v>
+        <v>7500</v>
       </c>
       <c r="G79" s="19">
-        <v>9816.98</v>
+        <v>7561.42</v>
       </c>
       <c r="H79" s="20">
-        <v>3.1224041236500001E-2</v>
+        <v>2.3714823364999998E-2</v>
       </c>
       <c r="I79" s="19">
-        <v>6.21</v>
-      </c>
-      <c r="J79" s="15">
-        <v>8.3699999999999992</v>
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D80" s="22">
-        <v>6.58</v>
+        <v>169</v>
+      </c>
+      <c r="D80" s="21">
+        <v>8</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F80" s="18">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="G80" s="19">
-        <v>7877.3</v>
+        <v>6465.79</v>
       </c>
       <c r="H80" s="20">
-        <v>2.5054664472399998E-2</v>
+        <v>2.0278607426299999E-2</v>
       </c>
       <c r="I80" s="19">
-        <v>7.89</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="J80" s="15" t="s">
         <v>13</v>
@@ -3862,28 +3840,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B81" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="D81" s="22">
-        <v>9.5</v>
+        <v>172</v>
+      </c>
+      <c r="D81" s="21">
+        <v>8.4</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F81" s="18">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="G81" s="19">
-        <v>7511.6</v>
+        <v>5139.09</v>
       </c>
       <c r="H81" s="20">
-        <v>2.3891513291500001E-2</v>
+        <v>1.6117688424499999E-2</v>
       </c>
       <c r="I81" s="19">
-        <v>9.3000000000000007</v>
+        <v>7.22</v>
       </c>
       <c r="J81" s="15" t="s">
         <v>13</v>
@@ -3891,28 +3869,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="D82" s="22">
-        <v>8</v>
+        <v>175</v>
+      </c>
+      <c r="D82" s="21">
+        <v>8.42</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F82" s="18">
-        <v>650</v>
+        <v>5000</v>
       </c>
       <c r="G82" s="19">
-        <v>6362.54</v>
+        <v>5125.88</v>
       </c>
       <c r="H82" s="20">
-        <v>2.0236794954099999E-2</v>
+        <v>1.6076258003199999E-2</v>
       </c>
       <c r="I82" s="19">
-        <v>9.3800000000000008</v>
+        <v>7.28</v>
       </c>
       <c r="J82" s="15" t="s">
         <v>13</v>
@@ -3920,28 +3898,28 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="D83" s="22">
-        <v>8.42</v>
+        <v>178</v>
+      </c>
+      <c r="D83" s="21">
+        <v>7.62</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F83" s="18">
         <v>5000</v>
       </c>
       <c r="G83" s="19">
-        <v>5026.59</v>
+        <v>5116.67</v>
       </c>
       <c r="H83" s="20">
-        <v>1.5987651338700001E-2</v>
+        <v>1.6047372750999999E-2</v>
       </c>
       <c r="I83" s="19">
-        <v>8.1999999999999993</v>
+        <v>6.61</v>
       </c>
       <c r="J83" s="15" t="s">
         <v>13</v>
@@ -3949,28 +3927,28 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" s="16" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="D84" s="22">
-        <v>8.4</v>
+        <v>180</v>
+      </c>
+      <c r="D84" s="21">
+        <v>8.73</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F84" s="18">
         <v>5000</v>
       </c>
       <c r="G84" s="19">
-        <v>5021.6899999999996</v>
+        <v>5100.91</v>
       </c>
       <c r="H84" s="20">
-        <v>1.59720663215E-2</v>
+        <v>1.59979447843E-2</v>
       </c>
       <c r="I84" s="19">
-        <v>8.2200000000000006</v>
+        <v>7.61</v>
       </c>
       <c r="J84" s="15" t="s">
         <v>13</v>
@@ -3978,28 +3956,28 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="16" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D85" s="22">
+        <v>182</v>
+      </c>
+      <c r="D85" s="21">
         <v>8.73</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F85" s="18">
         <v>5000</v>
       </c>
       <c r="G85" s="19">
-        <v>5019.5200000000004</v>
+        <v>5081.8999999999996</v>
       </c>
       <c r="H85" s="20">
-        <v>1.5965164385300001E-2</v>
+        <v>1.59383238676E-2</v>
       </c>
       <c r="I85" s="19">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="J85" s="15" t="s">
         <v>13</v>
@@ -4007,28 +3985,28 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="D86" s="22">
-        <v>8.73</v>
+        <v>184</v>
+      </c>
+      <c r="D86" s="21">
+        <v>8.25</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F86" s="18">
         <v>5000</v>
       </c>
       <c r="G86" s="19">
-        <v>5016.24</v>
+        <v>5054.13</v>
       </c>
       <c r="H86" s="20">
-        <v>1.5954731965599999E-2</v>
+        <v>1.58512290302E-2</v>
       </c>
       <c r="I86" s="19">
-        <v>8.5299999999999994</v>
+        <v>7.55</v>
       </c>
       <c r="J86" s="15" t="s">
         <v>13</v>
@@ -4036,28 +4014,28 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="16" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="D87" s="22">
-        <v>8.25</v>
+        <v>186</v>
+      </c>
+      <c r="D87" s="21">
+        <v>10</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F87" s="18">
         <v>5000</v>
       </c>
       <c r="G87" s="19">
-        <v>5013.7700000000004</v>
+        <v>5022.6899999999996</v>
       </c>
       <c r="H87" s="20">
-        <v>1.59468758447E-2</v>
+        <v>1.57526240001E-2</v>
       </c>
       <c r="I87" s="19">
-        <v>8.09</v>
+        <v>9.6</v>
       </c>
       <c r="J87" s="15" t="s">
         <v>13</v>
@@ -4065,28 +4043,28 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D88" s="22">
-        <v>8.5</v>
+        <v>189</v>
+      </c>
+      <c r="D88" s="21">
+        <v>8.9500000000000011</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="F88" s="18">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="G88" s="19">
-        <v>4980.82</v>
+        <v>4071.96</v>
       </c>
       <c r="H88" s="20">
-        <v>1.5842074555700001E-2</v>
+        <v>1.27708568165E-2</v>
       </c>
       <c r="I88" s="19">
-        <v>9.25</v>
+        <v>7.59</v>
       </c>
       <c r="J88" s="15" t="s">
         <v>13</v>
@@ -4094,28 +4072,28 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="16" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="D89" s="22">
-        <v>10</v>
+        <v>191</v>
+      </c>
+      <c r="D89" s="21">
+        <v>9.9500000000000011</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F89" s="18">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="G89" s="19">
-        <v>4961.6000000000004</v>
+        <v>4040.01</v>
       </c>
       <c r="H89" s="20">
-        <v>1.57809431209E-2</v>
+        <v>1.26706522773E-2</v>
       </c>
       <c r="I89" s="19">
-        <v>10.44</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="J89" s="15" t="s">
         <v>13</v>
@@ -4123,28 +4101,28 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="D90" s="22">
-        <v>8.9500000000000011</v>
+        <v>194</v>
+      </c>
+      <c r="D90" s="21">
+        <v>8.92</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F90" s="18">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="G90" s="19">
-        <v>4037.8</v>
+        <v>3527.82</v>
       </c>
       <c r="H90" s="20">
-        <v>1.2842690288100001E-2</v>
+        <v>1.10642747213E-2</v>
       </c>
       <c r="I90" s="19">
-        <v>8.35</v>
+        <v>8.48</v>
       </c>
       <c r="J90" s="15" t="s">
         <v>13</v>
@@ -4152,28 +4130,28 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="D91" s="22">
-        <v>9.9500000000000011</v>
+        <v>197</v>
+      </c>
+      <c r="D91" s="21">
+        <v>8.6</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F91" s="18">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="G91" s="19">
-        <v>3990.67</v>
+        <v>3031.37</v>
       </c>
       <c r="H91" s="20">
-        <v>1.2692787867699999E-2</v>
+        <v>9.5072624061999997E-3</v>
       </c>
       <c r="I91" s="19">
-        <v>10.47</v>
+        <v>8.02</v>
       </c>
       <c r="J91" s="15" t="s">
         <v>13</v>
@@ -4181,28 +4159,28 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B92" s="16" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="D92" s="22">
-        <v>8.92</v>
+        <v>199</v>
+      </c>
+      <c r="D92" s="21">
+        <v>8.5</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F92" s="18">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="G92" s="19">
-        <v>3494.25</v>
+        <v>3014.55</v>
       </c>
       <c r="H92" s="20">
-        <v>1.11138665955E-2</v>
+        <v>9.4545099697000007E-3</v>
       </c>
       <c r="I92" s="19">
-        <v>9.35</v>
+        <v>7.99</v>
       </c>
       <c r="J92" s="15" t="s">
         <v>13</v>
@@ -4210,28 +4188,28 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B93" s="16" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="D93" s="22">
-        <v>8.6</v>
+        <v>201</v>
+      </c>
+      <c r="D93" s="21">
+        <v>9.4</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="F93" s="18">
         <v>3000</v>
       </c>
       <c r="G93" s="19">
-        <v>2982.08</v>
+        <v>3013.87</v>
       </c>
       <c r="H93" s="20">
-        <v>9.4848506252000007E-3</v>
+        <v>9.4523772908999999E-3</v>
       </c>
       <c r="I93" s="19">
-        <v>8.84</v>
+        <v>9.06</v>
       </c>
       <c r="J93" s="15" t="s">
         <v>13</v>
@@ -4239,28 +4217,28 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="D94" s="22">
-        <v>8.5</v>
+        <v>203</v>
+      </c>
+      <c r="D94" s="21">
+        <v>7.58</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F94" s="18">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G94" s="19">
-        <v>2980.68</v>
+        <v>2562.5</v>
       </c>
       <c r="H94" s="20">
-        <v>9.4803977630999996E-3</v>
+        <v>8.0367490328999997E-3</v>
       </c>
       <c r="I94" s="19">
-        <v>8.94</v>
+        <v>7.21</v>
       </c>
       <c r="J94" s="15" t="s">
         <v>13</v>
@@ -4268,28 +4246,28 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="D95" s="22">
+        <v>205</v>
+      </c>
+      <c r="D95" s="21">
         <v>9.3000000000000007</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="F95" s="18">
         <v>2500</v>
       </c>
       <c r="G95" s="19">
-        <v>2522.62</v>
+        <v>2538.85</v>
       </c>
       <c r="H95" s="20">
-        <v>8.0234849112E-3</v>
+        <v>7.9625757199000002E-3</v>
       </c>
       <c r="I95" s="19">
-        <v>9.1999999999999993</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="J95" s="15" t="s">
         <v>13</v>
@@ -4297,28 +4275,28 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="16" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="D96" s="22">
-        <v>8.4600000000000009</v>
+        <v>207</v>
+      </c>
+      <c r="D96" s="21">
+        <v>8</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F96" s="18">
         <v>2500</v>
       </c>
       <c r="G96" s="19">
-        <v>2507.34</v>
+        <v>2533.0500000000002</v>
       </c>
       <c r="H96" s="20">
-        <v>7.9748851025000008E-3</v>
+        <v>7.9443852245000002E-3</v>
       </c>
       <c r="I96" s="19">
-        <v>8.34</v>
+        <v>7.56</v>
       </c>
       <c r="J96" s="15" t="s">
         <v>13</v>
@@ -4326,28 +4304,28 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B97" s="16" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="D97" s="22">
-        <v>9.9500000000000011</v>
+        <v>210</v>
+      </c>
+      <c r="D97" s="21">
+        <v>8.4600000000000009</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F97" s="18">
         <v>2500</v>
       </c>
       <c r="G97" s="19">
-        <v>2502.85</v>
+        <v>2530.83</v>
       </c>
       <c r="H97" s="20">
-        <v>7.9606041378000002E-3</v>
+        <v>7.9374226555999992E-3</v>
       </c>
       <c r="I97" s="19">
-        <v>8.98</v>
+        <v>7.89</v>
       </c>
       <c r="J97" s="15" t="s">
         <v>13</v>
@@ -4355,28 +4333,28 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B98" s="16" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="D98" s="22">
+        <v>213</v>
+      </c>
+      <c r="D98" s="21">
         <v>8.5</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="F98" s="18">
         <v>2500</v>
       </c>
       <c r="G98" s="19">
-        <v>2502.0500000000002</v>
+        <v>2526.59</v>
       </c>
       <c r="H98" s="20">
-        <v>7.9580596451999993E-3</v>
+        <v>7.9241247761999995E-3</v>
       </c>
       <c r="I98" s="19">
-        <v>8.3800000000000008</v>
+        <v>7.5</v>
       </c>
       <c r="J98" s="15" t="s">
         <v>13</v>
@@ -4384,28 +4362,28 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="D99" s="22">
-        <v>8.75</v>
+        <v>215</v>
+      </c>
+      <c r="D99" s="21">
+        <v>8.6</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F99" s="18">
         <v>2500</v>
       </c>
       <c r="G99" s="19">
-        <v>2497.41</v>
+        <v>2523.89</v>
       </c>
       <c r="H99" s="20">
-        <v>7.9433015881000008E-3</v>
+        <v>7.915656787E-3</v>
       </c>
       <c r="I99" s="19">
-        <v>8.67</v>
+        <v>7.93</v>
       </c>
       <c r="J99" s="15" t="s">
         <v>13</v>
@@ -4413,28 +4391,28 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B100" s="16" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="D100" s="22">
-        <v>8</v>
+        <v>217</v>
+      </c>
+      <c r="D100" s="21">
+        <v>8.75</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="F100" s="18">
         <v>2500</v>
       </c>
       <c r="G100" s="19">
-        <v>2492.96</v>
+        <v>2522.5100000000002</v>
       </c>
       <c r="H100" s="20">
-        <v>7.9291478479999993E-3</v>
+        <v>7.9113287035999999E-3</v>
       </c>
       <c r="I100" s="19">
-        <v>8.3800000000000008</v>
+        <v>7.96</v>
       </c>
       <c r="J100" s="15" t="s">
         <v>13</v>
@@ -4442,28 +4420,28 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B101" s="16" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="D101" s="22">
+        <v>219</v>
+      </c>
+      <c r="D101" s="21">
         <v>7.45</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F101" s="18">
         <v>250</v>
       </c>
       <c r="G101" s="19">
-        <v>2472.4699999999998</v>
+        <v>2514.4499999999998</v>
       </c>
       <c r="H101" s="20">
-        <v>7.8639770312000003E-3</v>
+        <v>7.8860501877E-3</v>
       </c>
       <c r="I101" s="19">
-        <v>8.0299999999999994</v>
+        <v>7.07</v>
       </c>
       <c r="J101" s="15" t="s">
         <v>13</v>
@@ -4471,28 +4449,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B102" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="D102" s="22">
+        <v>221</v>
+      </c>
+      <c r="D102" s="21">
         <v>8.75</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="F102" s="18">
         <v>2500</v>
       </c>
       <c r="G102" s="19">
-        <v>2472.35</v>
+        <v>2487.1</v>
       </c>
       <c r="H102" s="20">
-        <v>7.8635953572999996E-3</v>
+        <v>7.8002725931000001E-3</v>
       </c>
       <c r="I102" s="19">
-        <v>9.8800000000000008</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="J102" s="15" t="s">
         <v>13</v>
@@ -4500,28 +4478,28 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B103" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="D103" s="21">
+        <v>8.75</v>
+      </c>
+      <c r="E103" s="17" t="s">
         <v>211</v>
-      </c>
-      <c r="C103" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="D103" s="22">
-        <v>8.75</v>
-      </c>
-      <c r="E103" s="17" t="s">
-        <v>213</v>
       </c>
       <c r="F103" s="18">
         <v>200</v>
       </c>
       <c r="G103" s="19">
-        <v>2012.55</v>
+        <v>2032.79</v>
       </c>
       <c r="H103" s="20">
-        <v>6.4011482339999997E-3</v>
+        <v>6.3754236358000002E-3</v>
       </c>
       <c r="I103" s="19">
-        <v>8.33</v>
+        <v>7.43</v>
       </c>
       <c r="J103" s="15" t="s">
         <v>13</v>
@@ -4529,28 +4507,28 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B104" s="16" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="D104" s="22">
+        <v>224</v>
+      </c>
+      <c r="D104" s="21">
         <v>7.99</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F104" s="18">
         <v>1900</v>
       </c>
       <c r="G104" s="19">
-        <v>1901.7</v>
+        <v>1915.94</v>
       </c>
       <c r="H104" s="20">
-        <v>6.0485769777999998E-3</v>
+        <v>6.0089478798999998E-3</v>
       </c>
       <c r="I104" s="19">
-        <v>8.0500000000000007</v>
+        <v>7.09</v>
       </c>
       <c r="J104" s="15" t="s">
         <v>13</v>
@@ -4558,28 +4536,28 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B105" s="16" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C105" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="D105" s="22">
-        <v>9.4</v>
+        <v>226</v>
+      </c>
+      <c r="D105" s="21">
+        <v>10.81</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F105" s="18">
         <v>1500</v>
       </c>
       <c r="G105" s="19">
-        <v>1499.21</v>
+        <v>1513.21</v>
       </c>
       <c r="H105" s="20">
-        <v>4.7684109432999996E-3</v>
+        <v>4.7458688795999999E-3</v>
       </c>
       <c r="I105" s="19">
-        <v>9.66</v>
+        <v>10.62</v>
       </c>
       <c r="J105" s="15" t="s">
         <v>13</v>
@@ -4587,28 +4565,28 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="16" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="D106" s="22">
-        <v>10.81</v>
+        <v>229</v>
+      </c>
+      <c r="D106" s="21">
+        <v>9.4</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F106" s="18">
         <v>1500</v>
       </c>
       <c r="G106" s="19">
-        <v>1494.27</v>
+        <v>1506.41</v>
       </c>
       <c r="H106" s="20">
-        <v>4.7526987014000002E-3</v>
+        <v>4.7245420919999996E-3</v>
       </c>
       <c r="I106" s="19">
-        <v>11.49</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="J106" s="15" t="s">
         <v>13</v>
@@ -4616,28 +4594,28 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="D107" s="22">
-        <v>9.5399999999999991</v>
+        <v>232</v>
+      </c>
+      <c r="D107" s="21">
+        <v>9.58</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F107" s="18">
         <v>125</v>
       </c>
       <c r="G107" s="19">
-        <v>1329.57</v>
+        <v>1330.65</v>
       </c>
       <c r="H107" s="20">
-        <v>4.2288512868999999E-3</v>
+        <v>4.1733073563000002E-3</v>
       </c>
       <c r="I107" s="19">
-        <v>9.4700000000000006</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="J107" s="15" t="s">
         <v>13</v>
@@ -4645,28 +4623,28 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" s="16" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="D108" s="22">
-        <v>8.7900000000000009</v>
+        <v>233</v>
+      </c>
+      <c r="D108" s="21">
+        <v>8.9</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="F108" s="18">
-        <v>1304</v>
+        <v>1000</v>
       </c>
       <c r="G108" s="19">
-        <v>1303.51</v>
+        <v>1004.88</v>
       </c>
       <c r="H108" s="20">
-        <v>4.1459644403999997E-3</v>
+        <v>3.151597412E-3</v>
       </c>
       <c r="I108" s="19">
-        <v>9.14</v>
+        <v>7.58</v>
       </c>
       <c r="J108" s="15" t="s">
         <v>13</v>
@@ -4674,28 +4652,28 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B109" s="16" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="D109" s="22">
-        <v>7.17</v>
+        <v>235</v>
+      </c>
+      <c r="D109" s="21">
+        <v>9.75</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>182</v>
+        <v>236</v>
       </c>
       <c r="F109" s="18">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="G109" s="19">
-        <v>1195.9000000000001</v>
+        <v>1001.71</v>
       </c>
       <c r="H109" s="20">
-        <v>3.8036983791999998E-3</v>
+        <v>3.1416553653E-3</v>
       </c>
       <c r="I109" s="19">
-        <v>8.0299999999999994</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="J109" s="15" t="s">
         <v>13</v>
@@ -4703,28 +4681,28 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="16" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="C110" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="D110" s="22">
-        <v>8.9</v>
+        <v>238</v>
+      </c>
+      <c r="D110" s="21">
+        <v>8.7900000000000009</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F110" s="18">
-        <v>1000</v>
+        <v>904</v>
       </c>
       <c r="G110" s="19">
-        <v>1003.05</v>
+        <v>908.11</v>
       </c>
       <c r="H110" s="20">
-        <v>3.1903166312000002E-3</v>
+        <v>2.8480984055000002E-3</v>
       </c>
       <c r="I110" s="19">
-        <v>8.39</v>
+        <v>7.95</v>
       </c>
       <c r="J110" s="15" t="s">
         <v>13</v>
@@ -4732,28 +4710,28 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" s="16" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="C111" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="D111" s="22">
-        <v>8.85</v>
+        <v>239</v>
+      </c>
+      <c r="D111" s="21">
+        <v>9.58</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F111" s="18">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G111" s="19">
-        <v>999.78</v>
+        <v>634.61</v>
       </c>
       <c r="H111" s="20">
-        <v>3.1799160177E-3</v>
+        <v>1.99032246E-3</v>
       </c>
       <c r="I111" s="19">
-        <v>8.5</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="J111" s="15" t="s">
         <v>13</v>
@@ -4761,28 +4739,28 @@
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="D112" s="22">
-        <v>9.75</v>
+        <v>240</v>
+      </c>
+      <c r="D112" s="21">
+        <v>9.58</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>245</v>
+        <v>161</v>
       </c>
       <c r="F112" s="18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="G112" s="19">
-        <v>995.19</v>
+        <v>633.71</v>
       </c>
       <c r="H112" s="20">
-        <v>3.1653169913999999E-3</v>
+        <v>1.9874997969000002E-3</v>
       </c>
       <c r="I112" s="19">
-        <v>10.199999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="J112" s="15" t="s">
         <v>13</v>
@@ -4790,28 +4768,28 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C113" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="D113" s="22">
-        <v>9.5399999999999991</v>
+        <v>241</v>
+      </c>
+      <c r="D113" s="21">
+        <v>9.58</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F113" s="18">
         <v>60</v>
       </c>
       <c r="G113" s="19">
-        <v>633.64</v>
+        <v>631.36</v>
       </c>
       <c r="H113" s="20">
-        <v>2.0153653658E-3</v>
+        <v>1.9801295099999999E-3</v>
       </c>
       <c r="I113" s="19">
-        <v>9.2799999999999994</v>
+        <v>8.25</v>
       </c>
       <c r="J113" s="15" t="s">
         <v>13</v>
@@ -4819,28 +4797,28 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B114" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="D114" s="22">
-        <v>9.5399999999999991</v>
+        <v>242</v>
+      </c>
+      <c r="D114" s="21">
+        <v>9.58</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F114" s="18">
         <v>60</v>
       </c>
       <c r="G114" s="19">
-        <v>632.96</v>
+        <v>631.21</v>
       </c>
       <c r="H114" s="20">
-        <v>2.0132025470999998E-3</v>
+        <v>1.9796590661E-3</v>
       </c>
       <c r="I114" s="19">
-        <v>9.36</v>
+        <v>7.06</v>
       </c>
       <c r="J114" s="15" t="s">
         <v>13</v>
@@ -4848,28 +4826,28 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B115" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="D115" s="22">
-        <v>9.5399999999999991</v>
+        <v>243</v>
+      </c>
+      <c r="D115" s="21">
+        <v>9.58</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F115" s="18">
         <v>60</v>
       </c>
       <c r="G115" s="19">
-        <v>629.1</v>
+        <v>631.16</v>
       </c>
       <c r="H115" s="20">
-        <v>2.0009253703000001E-3</v>
+        <v>1.9795022514999998E-3</v>
       </c>
       <c r="I115" s="19">
-        <v>9.3000000000000007</v>
+        <v>7.64</v>
       </c>
       <c r="J115" s="15" t="s">
         <v>13</v>
@@ -4877,28 +4855,28 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="D116" s="22">
-        <v>9.5399999999999991</v>
+        <v>244</v>
+      </c>
+      <c r="D116" s="21">
+        <v>9.58</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F116" s="18">
         <v>60</v>
       </c>
       <c r="G116" s="19">
-        <v>626.54999999999995</v>
+        <v>631.09</v>
       </c>
       <c r="H116" s="20">
-        <v>1.9928148001E-3</v>
+        <v>1.9792827110999998E-3</v>
       </c>
       <c r="I116" s="19">
-        <v>9.24</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="J116" s="15" t="s">
         <v>13</v>
@@ -4906,28 +4884,28 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B117" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="D117" s="22">
-        <v>9.5399999999999991</v>
+        <v>245</v>
+      </c>
+      <c r="D117" s="21">
+        <v>9.58</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F117" s="18">
         <v>60</v>
       </c>
       <c r="G117" s="19">
-        <v>623.77</v>
+        <v>630.41999999999996</v>
       </c>
       <c r="H117" s="20">
-        <v>1.9839726883E-3</v>
+        <v>1.9771813952000001E-3</v>
       </c>
       <c r="I117" s="19">
-        <v>9.18</v>
+        <v>8.01</v>
       </c>
       <c r="J117" s="15" t="s">
         <v>13</v>
@@ -4935,28 +4913,28 @@
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B118" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="D118" s="22">
-        <v>9.5399999999999991</v>
+        <v>246</v>
+      </c>
+      <c r="D118" s="21">
+        <v>9.58</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F118" s="18">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G118" s="19">
-        <v>620.74</v>
+        <v>529.67999999999995</v>
       </c>
       <c r="H118" s="20">
-        <v>1.9743354225999999E-3</v>
+        <v>1.6612313084E-3</v>
       </c>
       <c r="I118" s="19">
-        <v>9.1199999999999992</v>
+        <v>8.93</v>
       </c>
       <c r="J118" s="15" t="s">
         <v>13</v>
@@ -4964,28 +4942,28 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B119" s="16" t="s">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="C119" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="D119" s="22">
-        <v>9.5399999999999991</v>
+        <v>247</v>
+      </c>
+      <c r="D119" s="21">
+        <v>7.44</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F119" s="18">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="G119" s="19">
-        <v>617.42999999999995</v>
+        <v>509.85</v>
       </c>
       <c r="H119" s="20">
-        <v>1.9638075843999999E-3</v>
+        <v>1.5990386319000001E-3</v>
       </c>
       <c r="I119" s="19">
-        <v>9.0399999999999991</v>
+        <v>6.61</v>
       </c>
       <c r="J119" s="15" t="s">
         <v>13</v>
@@ -4993,28 +4971,28 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B120" s="16" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C120" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="D120" s="22">
-        <v>9.5399999999999991</v>
+        <v>249</v>
+      </c>
+      <c r="D120" s="21">
+        <v>8.4499999999999993</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F120" s="18">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="G120" s="19">
-        <v>531.24</v>
+        <v>506.54</v>
       </c>
       <c r="H120" s="20">
-        <v>1.6896703126999999E-3</v>
+        <v>1.5886575043999999E-3</v>
       </c>
       <c r="I120" s="19">
-        <v>9.43</v>
+        <v>7.34</v>
       </c>
       <c r="J120" s="15" t="s">
         <v>13</v>
@@ -5022,28 +5000,28 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B121" s="16" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C121" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="D121" s="22">
+        <v>250</v>
+      </c>
+      <c r="D121" s="21">
         <v>8.4499999999999993</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>256</v>
+        <v>181</v>
       </c>
       <c r="F121" s="18">
         <v>500</v>
       </c>
       <c r="G121" s="19">
-        <v>500.95</v>
+        <v>504.23</v>
       </c>
       <c r="H121" s="20">
-        <v>1.5933294615E-3</v>
+        <v>1.5814126692E-3</v>
       </c>
       <c r="I121" s="19">
-        <v>8.2799999999999994</v>
+        <v>7.39</v>
       </c>
       <c r="J121" s="15" t="s">
         <v>13</v>
@@ -5051,28 +5029,28 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="16" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C122" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="D122" s="22">
+        <v>251</v>
+      </c>
+      <c r="D122" s="21">
         <v>8.4499999999999993</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>256</v>
+        <v>181</v>
       </c>
       <c r="F122" s="18">
         <v>500</v>
       </c>
       <c r="G122" s="19">
-        <v>500.72</v>
+        <v>501.27</v>
       </c>
       <c r="H122" s="20">
-        <v>1.5925979199E-3</v>
+        <v>1.5721292439999999E-3</v>
       </c>
       <c r="I122" s="19">
-        <v>8.32</v>
+        <v>7.3</v>
       </c>
       <c r="J122" s="15" t="s">
         <v>13</v>
@@ -5080,28 +5058,28 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B123" s="16" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="C123" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="D123" s="22">
-        <v>8.4499999999999993</v>
+        <v>252</v>
+      </c>
+      <c r="D123" s="21">
+        <v>9.75</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F123" s="18">
         <v>500</v>
       </c>
       <c r="G123" s="19">
-        <v>499.87</v>
+        <v>500.89</v>
       </c>
       <c r="H123" s="20">
-        <v>1.5898943965E-3</v>
+        <v>1.5709374529E-3</v>
       </c>
       <c r="I123" s="19">
-        <v>8.3800000000000008</v>
+        <v>9.6</v>
       </c>
       <c r="J123" s="15" t="s">
         <v>13</v>
@@ -5109,28 +5087,28 @@
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B124" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="C124" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="C124" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="D124" s="22">
-        <v>8.4499999999999993</v>
+      <c r="D124" s="21">
+        <v>7.99</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>256</v>
+        <v>176</v>
       </c>
       <c r="F124" s="18">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G124" s="19">
-        <v>499.34</v>
+        <v>405.22</v>
       </c>
       <c r="H124" s="20">
-        <v>1.5882086701E-3</v>
+        <v>1.270888368E-3</v>
       </c>
       <c r="I124" s="19">
-        <v>8.43</v>
+        <v>7.09</v>
       </c>
       <c r="J124" s="15" t="s">
         <v>13</v>
@@ -5138,139 +5116,139 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B125" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="C125" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J125" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H126" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I126" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J126" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J127" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B128" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H128" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I128" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J128" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J129" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B130" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="13">
+        <v>4297.26</v>
+      </c>
+      <c r="H130" s="14">
+        <v>1.3477463472799999E-2</v>
+      </c>
+      <c r="I130" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C131" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="D131" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="D125" s="22">
-        <v>7.99</v>
-      </c>
-      <c r="E125" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="F125" s="18">
-        <v>400</v>
-      </c>
-      <c r="G125" s="19">
-        <v>400.71</v>
-      </c>
-      <c r="H125" s="20">
-        <v>1.2745045384E-3</v>
-      </c>
-      <c r="I125" s="19">
-        <v>8.02</v>
-      </c>
-      <c r="J125" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J126" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="C127" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D127" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H127" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="I127" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J127" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="128" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J128" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="129" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G129" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H129" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="I129" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J129" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J130" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="C131" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D131" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F131" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" s="13">
-        <v>4762.04</v>
-      </c>
-      <c r="H131" s="14">
-        <v>1.5146219440999999E-2</v>
-      </c>
-      <c r="I131" s="13" t="s">
-        <v>13</v>
+      <c r="F131" s="18">
+        <v>16</v>
+      </c>
+      <c r="G131" s="19">
+        <v>1594.24</v>
+      </c>
+      <c r="H131" s="20">
+        <v>5.0000026452000001E-3</v>
+      </c>
+      <c r="I131" s="19">
+        <v>7.76</v>
       </c>
       <c r="J131" s="15" t="s">
         <v>13</v>
@@ -5278,28 +5256,28 @@
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B132" s="16" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D132" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F132" s="18">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G132" s="19">
-        <v>1626.7</v>
+        <v>1427.55</v>
       </c>
       <c r="H132" s="20">
-        <v>5.1739076455999998E-3</v>
+        <v>4.4772140806999998E-3</v>
       </c>
       <c r="I132" s="19">
-        <v>8.35</v>
+        <v>7.58</v>
       </c>
       <c r="J132" s="15" t="s">
         <v>13</v>
@@ -5307,28 +5285,28 @@
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B133" s="16" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D133" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F133" s="18">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G133" s="19">
-        <v>1595.17</v>
+        <v>1275.47</v>
       </c>
       <c r="H133" s="20">
-        <v>5.0736228308999997E-3</v>
+        <v>4.0002467469E-3</v>
       </c>
       <c r="I133" s="19">
-        <v>8.41</v>
+        <v>7.39</v>
       </c>
       <c r="J133" s="15" t="s">
         <v>13</v>
@@ -5336,213 +5314,213 @@
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B134" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J134" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B135" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D135" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H135" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I135" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J135" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B136" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J136" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B137" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C134" s="17" t="s">
+      <c r="C137" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F137" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G137" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H137" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I137" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J137" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B138" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J138" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B139" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F139" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H139" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I139" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J139" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B140" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J140" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B141" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F141" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" s="13">
+        <v>35802.339999999997</v>
+      </c>
+      <c r="H141" s="14">
+        <v>0.1122866034626</v>
+      </c>
+      <c r="I141" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J141" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B142" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J142" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B143" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F143" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G143" s="13">
+        <v>28499.06</v>
+      </c>
+      <c r="H143" s="14">
+        <v>8.9381382593300002E-2</v>
+      </c>
+      <c r="I143" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J143" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B144" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="D134" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E134" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="F134" s="18">
-        <v>16</v>
-      </c>
-      <c r="G134" s="19">
-        <v>1540.17</v>
-      </c>
-      <c r="H134" s="20">
-        <v>4.8986889644999998E-3</v>
-      </c>
-      <c r="I134" s="19">
-        <v>8.41</v>
-      </c>
-      <c r="J134" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="135" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B135" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J135" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B136" s="11" t="s">
+      <c r="C144" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="C136" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E136" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F136" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G136" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H136" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="I136" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J136" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="137" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B137" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J137" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="138" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B138" s="11" t="s">
+      <c r="D144" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="C138" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E138" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F138" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G138" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H138" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="I138" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J138" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="139" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B139" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J139" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="140" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="C140" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D140" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E140" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F140" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G140" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H140" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="I140" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J140" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="141" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B141" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J141" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="142" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B142" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="C142" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D142" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E142" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F142" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G142" s="13">
-        <v>36883.629999999997</v>
-      </c>
-      <c r="H142" s="14">
-        <v>0.11731265461179999</v>
-      </c>
-      <c r="I142" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J142" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="143" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B143" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J143" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="144" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B144" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="C144" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E144" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F144" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G144" s="13">
-        <v>29809.750000000004</v>
-      </c>
-      <c r="H144" s="14">
-        <v>9.4813360447800005E-2</v>
-      </c>
-      <c r="I144" s="13" t="s">
-        <v>13</v>
+      <c r="F144" s="18">
+        <v>1500</v>
+      </c>
+      <c r="G144" s="19">
+        <v>7143.72</v>
+      </c>
+      <c r="H144" s="20">
+        <v>2.2404794068999999E-2</v>
+      </c>
+      <c r="I144" s="19">
+        <v>6.43</v>
       </c>
       <c r="J144" s="15" t="s">
         <v>13</v>
@@ -5550,28 +5528,28 @@
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B145" s="16" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D145" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F145" s="18">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="G145" s="19">
-        <v>14901.92</v>
+        <v>7048.52</v>
       </c>
       <c r="H145" s="20">
-        <v>4.7397281504499997E-2</v>
+        <v>2.2106219041500001E-2</v>
       </c>
       <c r="I145" s="19">
-        <v>7.28</v>
+        <v>6.48</v>
       </c>
       <c r="J145" s="15" t="s">
         <v>13</v>
@@ -5579,28 +5557,28 @@
     </row>
     <row r="146" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B146" s="16" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D146" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F146" s="18">
         <v>1000</v>
       </c>
       <c r="G146" s="19">
-        <v>4976.12</v>
+        <v>4770.24</v>
       </c>
       <c r="H146" s="20">
-        <v>1.5827125661600001E-2</v>
+        <v>1.49608670076E-2</v>
       </c>
       <c r="I146" s="19">
-        <v>7.3</v>
+        <v>6.37</v>
       </c>
       <c r="J146" s="15" t="s">
         <v>13</v>
@@ -5608,28 +5586,28 @@
     </row>
     <row r="147" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B147" s="16" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D147" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E147" s="17" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F147" s="18">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G147" s="19">
-        <v>4963.38</v>
+        <v>2394.5300000000002</v>
       </c>
       <c r="H147" s="20">
-        <v>1.5786604616899999E-2</v>
+        <v>7.5099460144000003E-3</v>
       </c>
       <c r="I147" s="19">
-        <v>7.28</v>
+        <v>6.43</v>
       </c>
       <c r="J147" s="15" t="s">
         <v>13</v>
@@ -5637,28 +5615,28 @@
     </row>
     <row r="148" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B148" s="16" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D148" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E148" s="17" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F148" s="18">
         <v>500</v>
       </c>
       <c r="G148" s="19">
-        <v>2485.13</v>
+        <v>2383.91</v>
       </c>
       <c r="H148" s="20">
-        <v>7.9042436265999994E-3</v>
+        <v>7.4766385901E-3</v>
       </c>
       <c r="I148" s="19">
-        <v>7.28</v>
+        <v>6.44</v>
       </c>
       <c r="J148" s="15" t="s">
         <v>13</v>
@@ -5666,28 +5644,28 @@
     </row>
     <row r="149" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B149" s="16" t="s">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="C149" s="17" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D149" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E149" s="17" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F149" s="18">
         <v>500</v>
       </c>
       <c r="G149" s="19">
-        <v>2483.1999999999998</v>
+        <v>2382.04</v>
       </c>
       <c r="H149" s="20">
-        <v>7.8981050381999995E-3</v>
+        <v>7.4707737235000004E-3</v>
       </c>
       <c r="I149" s="19">
-        <v>7.27</v>
+        <v>6.41</v>
       </c>
       <c r="J149" s="15" t="s">
         <v>13</v>
@@ -5695,35 +5673,35 @@
     </row>
     <row r="150" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B150" s="16" t="s">
-        <v>13</v>
+        <v>274</v>
+      </c>
+      <c r="C150" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="D150" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F150" s="18">
+        <v>500</v>
+      </c>
+      <c r="G150" s="19">
+        <v>2376.1</v>
+      </c>
+      <c r="H150" s="20">
+        <v>7.4521441472000004E-3</v>
+      </c>
+      <c r="I150" s="19">
+        <v>6.43</v>
       </c>
       <c r="J150" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="151" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B151" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="C151" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E151" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G151" s="13">
-        <v>7073.88</v>
-      </c>
-      <c r="H151" s="14">
-        <v>2.2499294164000001E-2</v>
-      </c>
-      <c r="I151" s="13" t="s">
+      <c r="B151" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J151" s="15" t="s">
@@ -5731,29 +5709,29 @@
       </c>
     </row>
     <row r="152" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B152" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="C152" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="D152" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E152" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="F152" s="18">
-        <v>1500</v>
-      </c>
-      <c r="G152" s="19">
-        <v>7073.88</v>
-      </c>
-      <c r="H152" s="20">
-        <v>2.2499294164000001E-2</v>
-      </c>
-      <c r="I152" s="19">
-        <v>8.76</v>
+      <c r="B152" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152" s="13">
+        <v>7303.28</v>
+      </c>
+      <c r="H152" s="14">
+        <v>2.29052208693E-2</v>
+      </c>
+      <c r="I152" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J152" s="15" t="s">
         <v>13</v>
@@ -5761,35 +5739,35 @@
     </row>
     <row r="153" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B153" s="16" t="s">
-        <v>13</v>
+        <v>281</v>
+      </c>
+      <c r="C153" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="D153" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E153" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F153" s="18">
+        <v>1500</v>
+      </c>
+      <c r="G153" s="19">
+        <v>7303.28</v>
+      </c>
+      <c r="H153" s="20">
+        <v>2.29052208693E-2</v>
+      </c>
+      <c r="I153" s="19">
+        <v>7.51</v>
       </c>
       <c r="J153" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="154" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B154" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="C154" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E154" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F154" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G154" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H154" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="I154" s="13" t="s">
+      <c r="B154" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J154" s="15" t="s">
@@ -5797,7 +5775,28 @@
       </c>
     </row>
     <row r="155" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B155" s="16" t="s">
+      <c r="B155" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H155" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I155" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J155" s="15" t="s">
@@ -5805,28 +5804,7 @@
       </c>
     </row>
     <row r="156" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B156" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="C156" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E156" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F156" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G156" s="13">
-        <v>4739.5200000000004</v>
-      </c>
-      <c r="H156" s="14">
-        <v>1.50745919744E-2</v>
-      </c>
-      <c r="I156" s="13" t="s">
+      <c r="B156" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J156" s="15" t="s">
@@ -5834,28 +5812,28 @@
       </c>
     </row>
     <row r="157" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B157" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="C157" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="D157" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E157" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="F157" s="18">
-        <v>778598</v>
-      </c>
-      <c r="G157" s="19">
-        <v>2911.96</v>
-      </c>
-      <c r="H157" s="20">
-        <v>9.2618258486000006E-3</v>
-      </c>
-      <c r="I157" s="19" t="s">
+      <c r="B157" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="13">
+        <v>4958.46</v>
+      </c>
+      <c r="H157" s="14">
+        <v>1.55511799454E-2</v>
+      </c>
+      <c r="I157" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J157" s="15" t="s">
@@ -5864,25 +5842,25 @@
     </row>
     <row r="158" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="16" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C158" s="17" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D158" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E158" s="17" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F158" s="18">
-        <v>493748</v>
+        <v>778598</v>
       </c>
       <c r="G158" s="19">
-        <v>1827.56</v>
+        <v>3075.31</v>
       </c>
       <c r="H158" s="20">
-        <v>5.8127661258000002E-3</v>
+        <v>9.6450710902000001E-3</v>
       </c>
       <c r="I158" s="19" t="s">
         <v>13</v>
@@ -5893,6 +5871,27 @@
     </row>
     <row r="159" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B159" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C159" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="D159" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="F159" s="18">
+        <v>493748</v>
+      </c>
+      <c r="G159" s="19">
+        <v>1883.15</v>
+      </c>
+      <c r="H159" s="20">
+        <v>5.9061088552000004E-3</v>
+      </c>
+      <c r="I159" s="19" t="s">
         <v>13</v>
       </c>
       <c r="J159" s="15" t="s">
@@ -5900,28 +5899,7 @@
       </c>
     </row>
     <row r="160" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B160" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="C160" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D160" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E160" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F160" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G160" s="13">
-        <v>915.35</v>
-      </c>
-      <c r="H160" s="14">
-        <v>2.9113766296E-3</v>
-      </c>
-      <c r="I160" s="13" t="s">
+      <c r="B160" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J160" s="15" t="s">
@@ -5929,28 +5907,28 @@
       </c>
     </row>
     <row r="161" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B161" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="C161" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="D161" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E161" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="F161" s="18">
-        <v>8389.57</v>
-      </c>
-      <c r="G161" s="19">
-        <v>915.35</v>
-      </c>
-      <c r="H161" s="20">
-        <v>2.9113766296E-3</v>
-      </c>
-      <c r="I161" s="19" t="s">
+      <c r="B161" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="13">
+        <v>938.87</v>
+      </c>
+      <c r="H161" s="14">
+        <v>2.9445707568999998E-3</v>
+      </c>
+      <c r="I161" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J161" s="15" t="s">
@@ -5959,6 +5937,27 @@
     </row>
     <row r="162" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B162" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C162" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="D162" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="F162" s="18">
+        <v>8389.57</v>
+      </c>
+      <c r="G162" s="19">
+        <v>938.87</v>
+      </c>
+      <c r="H162" s="20">
+        <v>2.9445707568999998E-3</v>
+      </c>
+      <c r="I162" s="19" t="s">
         <v>13</v>
       </c>
       <c r="J162" s="15" t="s">
@@ -5966,28 +5965,7 @@
       </c>
     </row>
     <row r="163" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B163" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="C163" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D163" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E163" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G163" s="13">
-        <v>3378.67</v>
-      </c>
-      <c r="H163" s="14">
-        <v>1.07462510267E-2</v>
-      </c>
-      <c r="I163" s="13" t="s">
+      <c r="B163" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J163" s="15" t="s">
@@ -5995,7 +5973,28 @@
       </c>
     </row>
     <row r="164" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B164" s="16" t="s">
+      <c r="B164" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="13">
+        <v>3080.6</v>
+      </c>
+      <c r="H164" s="14">
+        <v>9.6616620764000006E-3</v>
+      </c>
+      <c r="I164" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J164" s="15" t="s">
@@ -6003,28 +6002,7 @@
       </c>
     </row>
     <row r="165" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B165" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="C165" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D165" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E165" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F165" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G165" s="13">
-        <v>830.00000999999997</v>
-      </c>
-      <c r="H165" s="14">
-        <v>2.6399111069000001E-3</v>
-      </c>
-      <c r="I165" s="13" t="s">
+      <c r="B165" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J165" s="15" t="s">
@@ -6032,21 +6010,28 @@
       </c>
     </row>
     <row r="166" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B166" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="C166" s="17"/>
-      <c r="D166" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E166" s="17"/>
-      <c r="G166" s="19">
-        <v>830.00000999999997</v>
-      </c>
-      <c r="H166" s="20">
-        <v>2.6399111069000001E-3</v>
-      </c>
-      <c r="I166" s="19" t="s">
+      <c r="B166" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D166" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="13">
+        <v>800.00000999999997</v>
+      </c>
+      <c r="H166" s="14">
+        <v>2.5090338758000002E-3</v>
+      </c>
+      <c r="I166" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J166" s="15" t="s">
@@ -6055,6 +6040,20 @@
     </row>
     <row r="167" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B167" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="C167" s="17"/>
+      <c r="D167" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E167" s="17"/>
+      <c r="G167" s="19">
+        <v>800.00000999999997</v>
+      </c>
+      <c r="H167" s="20">
+        <v>2.5090338758000002E-3</v>
+      </c>
+      <c r="I167" s="19" t="s">
         <v>13</v>
       </c>
       <c r="J167" s="15" t="s">
@@ -6062,186 +6061,182 @@
       </c>
     </row>
     <row r="168" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B168" s="23" t="s">
+      <c r="B168" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J168" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B169" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="C169" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D169" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" s="23">
+        <v>6728.2213060099166</v>
+      </c>
+      <c r="H169" s="24">
+        <v>2.110166871212487E-2</v>
+      </c>
+      <c r="I169" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J169" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B170" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="C170" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="23">
+        <v>318847.83131600998</v>
+      </c>
+      <c r="H170" s="24">
+        <v>0.99999999999362488</v>
+      </c>
+      <c r="I170" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J170" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B172" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="C172" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H172" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="173" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B173" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D173" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E173" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F173" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G173" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="H173" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B174" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B175" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C175" s="17"/>
+      <c r="D175" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E175" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F175" s="18">
+        <v>-85000</v>
+      </c>
+      <c r="G175" s="19">
+        <v>-697</v>
+      </c>
+      <c r="H175" s="20">
+        <v>-2.1859957368999998E-3</v>
+      </c>
+      <c r="I175" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J175" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B179" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="C168" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D168" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E168" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F168" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G168" s="24">
-        <v>6161.6096796799684</v>
-      </c>
-      <c r="H168" s="25">
-        <v>1.9597712812094437E-2</v>
-      </c>
-      <c r="I168" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="J168" s="26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="169" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B169" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="C169" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D169" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E169" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F169" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G169" s="24">
-        <v>314404.52968968003</v>
-      </c>
-      <c r="H169" s="25">
-        <v>0.99999999999399425</v>
-      </c>
-      <c r="I169" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="J169" s="26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="171" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B171" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="C171" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D171" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E171" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F171" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G171" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H171" s="24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="172" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B172" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C172" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D172" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="E172" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F172" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="G172" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="H172" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="173" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B173" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="C173" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D173" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E173" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F173" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G173" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H173" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="174" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B174" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="C174" s="17"/>
-      <c r="D174" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E174" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="F174" s="18">
-        <v>4875</v>
-      </c>
-      <c r="G174" s="19">
-        <v>63.48</v>
-      </c>
-      <c r="H174" s="20">
-        <v>2.01905488E-4</v>
-      </c>
-      <c r="I174" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J174" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="178" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B178" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
-    </row>
-    <row r="182" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B182" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
+      <c r="C179" s="6"/>
+      <c r="D179" s="6"/>
+      <c r="E179" s="6"/>
+      <c r="F179" s="6"/>
+      <c r="G179" s="6"/>
+      <c r="H179" s="6"/>
+      <c r="I179" s="6"/>
     </row>
     <row r="183" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C183" s="6"/>
       <c r="D183" s="6"/>
@@ -6249,10 +6244,11 @@
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
+      <c r="I183" s="6"/>
     </row>
     <row r="184" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B184" s="4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="6"/>
@@ -6263,7 +6259,7 @@
     </row>
     <row r="185" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B185" s="4" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C185" s="6"/>
       <c r="D185" s="6"/>
@@ -6274,7 +6270,7 @@
     </row>
     <row r="186" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B186" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="6"/>
@@ -6285,7 +6281,7 @@
     </row>
     <row r="187" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C187" s="6"/>
       <c r="D187" s="6"/>
@@ -6296,7 +6292,7 @@
     </row>
     <row r="188" spans="2:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B188" s="7" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="6"/>
@@ -6307,7 +6303,7 @@
     </row>
     <row r="189" spans="2:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B189" s="7" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C189" s="6"/>
       <c r="D189" s="6"/>
@@ -6318,7 +6314,7 @@
     </row>
     <row r="190" spans="2:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="6"/>
@@ -6327,9 +6323,9 @@
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
     </row>
-    <row r="191" spans="2:9" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B191" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C191" s="5"/>
       <c r="D191" s="5"/>
@@ -6338,36 +6334,35 @@
       <c r="G191" s="5"/>
     </row>
     <row r="194" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B194" s="27" t="s">
-        <v>317</v>
+      <c r="B194" s="26" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="209" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B209" s="27" t="s">
-        <v>318</v>
+      <c r="B209" s="26" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="210" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B210" s="27" t="s">
-        <v>319</v>
+      <c r="B210" s="26" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B178:I178"/>
-    <mergeCell ref="B182:I182"/>
-    <mergeCell ref="B188:H188"/>
+    <mergeCell ref="B179:I179"/>
+    <mergeCell ref="B183:I183"/>
     <mergeCell ref="B189:H189"/>
     <mergeCell ref="B190:H190"/>
     <mergeCell ref="B191:G191"/>
-    <mergeCell ref="B183:H183"/>
     <mergeCell ref="B184:H184"/>
     <mergeCell ref="B185:H185"/>
     <mergeCell ref="B186:H186"/>
     <mergeCell ref="B187:H187"/>
+    <mergeCell ref="B188:H188"/>
   </mergeCells>
   <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
